--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_③人材_職員個票と職員票" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_自由回答" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_計画本文への反映方針" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_見える化との突合" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -180,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -236,6 +237,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -602,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -768,12 +775,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
+          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと、④介護老人保健施設・通所リハビリテーションの介護職員数が見える化システムの従事者数と一致しないこと。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
@@ -787,7 +794,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>19件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -917,34 +924,50 @@
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>③ 事業所の意見（自由回答）</t>
+          <t>③ 見える化システムとの突合</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>人材紹介会社への紹介料が経営を圧迫しているという記述が5法人から寄せられています（1人当たり年収の30％、正職員1人70〜80万円との具体的な記述を含む）。外国人材の定着、給与水準、記録業務の負担も繰り返し挙げられています。</t>
+          <t>介護職員361人のうち、見える化システムのM2系列で従事者数を確認できるサービスは232人分です。グループホーム・特定施設・住宅型有料老人ホーム・サービス付高齢者向け住宅の129人（35.7％）は、見える化に従事者数の系列がなく、今回の調査が唯一の把握手段です。特別養護老人ホーム・地域密着型特別養護老人ホームの差は未回答1施設ずつで説明できますが、介護老人保健施設と通所リハビリテーションは全施設が回答したうえで差が生じています（10シート）。</t>
         </is>
       </c>
       <c r="C22" s="8" t="n"/>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="9" t="n"/>
     </row>
-    <row r="24" ht="104" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>③ 事業所の意見（自由回答）</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>人材紹介会社への紹介料が経営を圧迫しているという記述が5法人から寄せられています（1人当たり年収の30％、正職員1人70〜80万円との具体的な記述を含む）。外国人材の定着、給与水準、記録業務の負担も繰り返し挙げられています。</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="n"/>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>注1）本書の数値は、提出された調査票の集計シートの値をそのまま合計したものです。点検で見つかった事項を反映する前の値であり、事業所への照会の結果により変わります。注2）個票データ（利用者票99票・職員個票317人）は、個人情報を含むおそれがあるため成果品に収録していません。本書には集計値のみを収録しています（別冊のヒアリングシート 項目10）。注3）自由回答は事業所の意見であり、個人に関する記述は含まれていません。同一法人が複数の事業所から同文を提出したものは1件に集約しています。注4）3調査はいずれも令和7年4月1日現在（居場所変更・採用離職は令和6年度）を対象としています。第10期計画の基準年度（令和7年度）とは1年のずれがあります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="C11:E11"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -962,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1120,12 +1143,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>介護職員348人（重複を除く）、介護福祉士66.9％、勤続1年未満19.9％、外国人職員11.6％を掲載する。採用と離職の差、紹介料の負担を課題として整理する。</t>
+          <t>介護職員348人（重複を除く）、介護福祉士67.1％、勤続1年未満19.9％、外国人職員11.6％を掲載する。採用と離職の差、紹介料の負担を課題として整理する。見える化M2系列との突合（10シート）により、グループホーム・特定施設・住宅型有料・サ高住の129人が見える化では把握できないことを明記する。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>No.1の重複の確認。No.22の小規模多機能3事業所の提出の有無。No.23の訪問系の回収状況。</t>
+          <t>No.1の重複の確認。No.31の老健・通所リハと見える化の乖離。No.22の小規模多機能3事業所の提出の有無。No.23の訪問系の回収状況。</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1235,41 +1258,914 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>第2章第3節　住まいの供給量</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム3施設・サービス付高齢者向け住宅1施設の定員121人・入居者115人を掲載する。これらは介護保険の指定サービスではないため見える化に現れず、今回の調査が唯一の把握手段である（10シート）。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>No.30（有料老人ホーム華の施設等票）の提出の有無。提出があれば定員・入居者数が増える。</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>第6章第5節　医療と介護の連携</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>入所前の居場所の57.0％、退去先の47.0％が病院・診療所であること、退去理由の最多が医療的ケアであることを掲載する。受け入れ可能な医療処置（気管切開0施設等）と併せて、医療対応力の強化を課題として整理する。</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>特になし。集計値のみで記述できる。</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>着手可</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="104" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>注1）No.8のみ、点検で見つかった事項の影響を受けずに着手できる。残る7件は重大3件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
+    <row r="15" ht="104" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>注1）No.9（医療と介護の連携）のみ、点検で見つかった事項の影響を受けずに着手できる。残る8件は重大4件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>見える化システム（K系列・M2系列）との突合</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>介護人材実態調査で把握した介護職員数及び回答事業所数を、見える化システムのK系列（サービス提供事業所数）及びM2系列（従事者数の実数）と突合する。調査は令和7年4月1日現在、見える化は令和6年度（介護サービス施設・事業所調査）であり、時点が異なる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>サービス区分</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>調査の
+回答事業所</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>見える化K
+（R6）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>回答率</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>調査の
+介護職員</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>見える化M2
+介護職員(R6)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>特養</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>-19</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>定員は見える化D25により令和2年度以降160人。回答2施設の定員は60人＋50人＝110人であり、未回答1施設は50人規模と推定される。介護職員の差19人は、回答した羽衣園（50人規模）の19人と同水準であり、未回答1施設分で説明できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>地密特養</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>1施設当たりでは調査11.0人・見える化11.0人で一致する。差11人は未回答1施設分で説明できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>老健</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>3施設すべてが回答しており未回答による差ではない。見える化の介護職員は令和4年度78人から令和5年度56人・令和6年度59人へ減っており、調査値77人は令和4年度の水準に近い。見える化の直近2年の値が実態より低いか、調査で介護職員の範囲を広く記入したかのいずれかである。第3章第5節で従事者数の推移を記述する前に確認を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>通所リハ</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>3施設すべてが回答している。調査23人は見える化の介護職員13人を上回るが、見える化の全職種合計22人とはほぼ一致する。調査で介護職員以外の職種を含めて記入した可能性がある。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>通所介護等</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>50％</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>通所介護2事業所・地域密着型通所介護4事業所の計6事業所に対し回答3事業所。見える化の従事者数は、通所介護が平成29年度まで、地域密着型通所介護が令和5年度までであり、令和6年度の値がない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>5事業所すべてが回答しており、回答率100％である。見える化には認知症対応型共同生活介護の従事者数の系列がないため、今回の調査が唯一の把握手段である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>3事業所のうち2事業所が回答。見える化には特定施設入居者生活介護の従事者数の系列がない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームは介護保険の指定サービスではないため、見える化のK系列にも従事者数の系列にも現れない。有料老人ホーム華の13人は、併設のヘルパーステーションフラワーと同一の数値である（No.1）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>サ高住</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>サービス付高齢者向け住宅も同様に見える化に現れない。介護職員0人は、介護を併設又は外部の事業所が提供しているためと考えられる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>23％</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>13事業所のうち回答3事業所（うち1事業所はNo.1の重複の疑い）。見える化の従事者数は平成29年度（訪問介護員53人）が最後であり、令和6年度の値がない。第3章第5節の訪問介護の人材は今回の調査のみが根拠となる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="n">
+        <v>361</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr"/>
+      <c r="G15" s="15" t="inlineStr"/>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>華の重複13人を除くと348人</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>【見える化に従事者数の系列があるサービスと、ないサービス】</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>調査の介護職員</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>把握の可否</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>系列あり</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養・老健・通所リハ・通所介護・地域密着型通所介護・訪問介護</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>232</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>見える化M2系列で確認できる。ただし通所介護は平成29年度まで、地域密着型通所介護は令和5年度まで、訪問介護は平成29年度までである。</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="9" t="n"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>系列なし</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム・特定施設・住宅型有料老人ホーム・サービス付高齢者向け住宅</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>見える化に従事者数の系列がない。今回の調査が唯一の把握手段である。介護職員361人の35.7％（華の重複を除くと348人中116人・33.3％）を占める。</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="9" t="n"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>未回収</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護（5事業所）</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査の事業所票が確認できない（No.22）。見える化にも従事者数の系列がないため、現時点で把握できていない。</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="9" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>【他の調査と見える化の事業所数の突合】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>調査</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>対象サービス</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>調査の回答</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>見える化K（R6）</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>回答率</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>見方</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>①在宅</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援10事業所すべてから事業所票を受領しており、回答率100％である。①在宅の事業所票15件のうち、残る5件は小規模多機能3件と地域包括支援センター2件である。</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="9" t="n"/>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>①在宅</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能型居宅介護</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>60％</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>5事業所のうち3事業所から回答。介護人材実態調査には5事業所とも回答がない（No.22）。</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>特養＋地域密着型特養</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>6施設のうち4施設から施設等票を受領。回答4施設の定員は60＋50＋24＋18＝152人である。未回答2施設分を含めた定員との突合を要する。</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n"/>
+      <c r="H27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>3施設すべてから受領している。</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n"/>
+      <c r="H28" s="9" t="n"/>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>5事業所すべてから受領している。</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n"/>
+      <c r="H29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>3事業所のうち2事業所から受領。</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n"/>
+      <c r="H30" s="9" t="n"/>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム・サ高住</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>見える化に事業所数の系列がない。受領した4施設の定員は31＋30＋30＋30＝121人である。介護人材実態調査には有料老人ホーム華からも回答があるが、居所変更実態調査の施設等票は受領していない（No.30）。</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n"/>
+      <c r="H31" s="9" t="n"/>
+    </row>
+    <row r="33" ht="104" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>注1）見える化のK系列は各年度の10月1日現在、M2系列は介護サービス施設・事業所調査（各年10月1日現在）による。今回の3調査は令和7年4月1日現在であり、半年のずれがある。注2）M2系列の従事者数は職種別の実人員である。本表では「介護職員」の実数を用いた。認定者1万対の系列は用いていない。注3）特養・地域密着型特養の差は未回答1施設ずつで説明できるのに対し、老健・通所リハは全施設が回答したうえで差が生じている。この2サービスは、調査での「介護職員」の範囲の解釈を確認する。注4）住宅型有料老人ホーム・サービス付高齢者向け住宅は介護保険の指定サービスではないため見える化に現れない。今回の居所変更実態調査で定員121人・入居者115人を把握したことは、第2章第3節の住まいの供給量の記述を初めて可能にするものである。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1882,7 +2778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1896,7 +2792,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>点検で見つかった事項（29件）</t>
+          <t>点検で見つかった事項（31件）</t>
         </is>
       </c>
     </row>
@@ -1965,7 +2861,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同一の職員が両方の事業所に従事しているのか、一方が他方の写しであるのかを確認する。確認できるまで、介護職員の総数は施設・通所系319人＋訪問系29人＝348人として扱う。</t>
+          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。</t>
         </is>
       </c>
     </row>
@@ -2809,17 +3705,77 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="104" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大3件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否に直結する。注2）要確認18件（No.4〜No.21）は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件（No.22〜No.29）は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
+    <row r="34" ht="90" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム華の施設等票</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査には有料老人ホーム華から事業所票が提出されているが、居所変更実態調査の施設等票は受領した18件に含まれていない。他の住宅型有料老人ホーム3施設（ひばりの森・びえいの郷・花時計）はいずれも提出している。</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>提出対象であったかどうかを確認する。対象であれば、住宅型有料老人ホームの定員・入居者数（現在121人・115人）と入退去の把握が1施設分不足する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>③人材</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>老健・通所リハの介護職員数と見える化の乖離</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設は3施設すべてが回答して77人であるのに対し、見える化M2b（令和6年度）の介護職員は59人である（＋18人）。見える化は令和4年度78人から令和5年度56人へ急減しており、調査値は令和4年度の水準に近い。通所リハビリテーションも調査23人に対し見える化M2gの介護職員は13人であるが、全職種の合計22人とはほぼ一致する。一方、特養・地域密着型特養は未回答1施設分で差が説明でき、地域密着型特養は1施設当たり11.0人で完全に一致する。</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>①調査で「介護職員」に支援相談員・その他の職員を含めて記入したのか、②見える化の令和5・6年度の値が実態より低いのかを確認する。第3章第5節では「介護老人福祉施設の従事者数は平成29年度116人から令和6年度105人へ9.5％減少」と記述しており、老健の従事者数の推移を同じ枠組みで記述できるかどうかが変わる。調査票の職種の範囲を事業所に照会する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="104" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大4件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認19件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>調査票の選択肢が「1.○○　2.○○　3.○○　4.○○」のまま配布されており、記入形式が事業所ごとに異なる。町名34件＋11件、「市街地」「郊外」17件、番号13件、未記入21件、区域外の市町村名1件。</t>
+          <t>調査票の選択肢が「1.○○　2.○○　3.○○　4.○○」のまま配布されており、記入形式が事業所ごとに異なる。内訳は、町名46件（美瑛町34・東川町11・「1.美瑛町」1）、「市街地」15件・「郊外」2件、番号13件（「1」10・「2」3）、未記入22件、区域外の市町村名1件で、計99票である。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -18,6 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_自由回答" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_計画本文への反映方針" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_見える化との突合" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_調査内クロス集計_①利用者票" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_調査内クロス集計_②施設等票" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_調査内クロス集計_③職員" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_記載内容の一覧" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_職員数の公表データ突合の検討" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -181,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -243,6 +248,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2171,6 +2179,8998 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>① 在宅生活改善調査　利用者票（99票）の調査内クロス集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>利用者票の中だけで組める掛け合わせを集計する。他の調査との接合は所在地区の記入形式が統一されていないためできない（02シートNo.3）。個票は収録せず度数のみを示す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【提出元 × 希望の方向】　最も差が大きい掛け合わせ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>施設等への入所・入居</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>在宅サービスの追加・変更</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能2事業所</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>5（14％）</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>31（86％）</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>他の8事業所</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>55（87％）</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>8（13％）</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="E8" s="15" t="inlineStr"/>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+      <c r="J8" s="15" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>【要支援・要介護度 × 希望の方向】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>施設等への入所・入居</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>在宅サービスの追加・変更</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>1（33％）</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>2（67％）</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="13" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>9（69％）</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>4（31％）</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="13" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>20（61％）</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>13（39％）</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>12（55％）</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>10（45％）</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>12（63％）</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>7（37％）</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>3（60％）</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>2（40％）</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>3（100％）</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>0（0％）</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="13" t="inlineStr"/>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E19" s="15" t="inlineStr"/>
+      <c r="F19" s="15" t="inlineStr"/>
+      <c r="G19" s="15" t="inlineStr"/>
+      <c r="H19" s="15" t="inlineStr"/>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>【要支援・要介護度 × 現在の居所】</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>自宅等</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>サ高住</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>軽費老人ホーム</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
+      <c r="I30" s="15" t="inlineStr"/>
+      <c r="J30" s="15" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>【要支援・要介護度 × 入所・入居の緊急度】（施設等を選んだ60票）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>3か月以内</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1年以内</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>1年より先</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="13" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F35" s="13" t="inlineStr"/>
+      <c r="G35" s="13" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="13" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" s="13" t="inlineStr"/>
+      <c r="G37" s="13" t="inlineStr"/>
+      <c r="H37" s="13" t="inlineStr"/>
+      <c r="I37" s="13" t="inlineStr"/>
+      <c r="J37" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" s="13" t="inlineStr"/>
+      <c r="G38" s="13" t="inlineStr"/>
+      <c r="H38" s="13" t="inlineStr"/>
+      <c r="I38" s="13" t="inlineStr"/>
+      <c r="J38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="13" t="inlineStr"/>
+      <c r="G39" s="13" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr"/>
+      <c r="I39" s="13" t="inlineStr"/>
+      <c r="J39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="13" t="inlineStr"/>
+      <c r="G40" s="13" t="inlineStr"/>
+      <c r="H40" s="13" t="inlineStr"/>
+      <c r="I40" s="13" t="inlineStr"/>
+      <c r="J40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="15" t="inlineStr"/>
+      <c r="G41" s="15" t="inlineStr"/>
+      <c r="H41" s="15" t="inlineStr"/>
+      <c r="I41" s="15" t="inlineStr"/>
+      <c r="J41" s="15" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>【世帯類型 × 希望の方向】</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>施設等への入所・入居</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>在宅サービスの追加・変更</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>独居</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>29（64％）</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>16（36％）</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="E45" s="13" t="inlineStr"/>
+      <c r="F45" s="13" t="inlineStr"/>
+      <c r="G45" s="13" t="inlineStr"/>
+      <c r="H45" s="13" t="inlineStr"/>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>夫婦のみ</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>11（65％）</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>6（35％）</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="13" t="inlineStr"/>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>単身の子と同居</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>8（57％）</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>6（43％）</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr"/>
+      <c r="F47" s="13" t="inlineStr"/>
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>その他の同居</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>12（55％）</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>10（45％）</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E48" s="13" t="inlineStr"/>
+      <c r="F48" s="13" t="inlineStr"/>
+      <c r="G48" s="13" t="inlineStr"/>
+      <c r="H48" s="13" t="inlineStr"/>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E49" s="15" t="inlineStr"/>
+      <c r="F49" s="15" t="inlineStr"/>
+      <c r="G49" s="15" t="inlineStr"/>
+      <c r="H49" s="15" t="inlineStr"/>
+      <c r="I49" s="15" t="inlineStr"/>
+      <c r="J49" s="15" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>【世帯類型 × 主な家族等介護者の年代】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>30代</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>40代</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>50代</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>60代</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>70代</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>80歳以上</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>介護者はいない</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>独居</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>夫婦のみ</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>単身の子と同居</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>その他の同居</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J57" s="15" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>【主な家族等介護者の勤務形態 × 就労継続が困難】</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>該当する</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>該当しない</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>フルタイム</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>20（67％）</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>10（33％）</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" s="13" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr"/>
+      <c r="G61" s="13" t="inlineStr"/>
+      <c r="H61" s="13" t="inlineStr"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>パートタイム</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>6（55％）</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>5（45％）</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E62" s="13" t="inlineStr"/>
+      <c r="F62" s="13" t="inlineStr"/>
+      <c r="G62" s="13" t="inlineStr"/>
+      <c r="H62" s="13" t="inlineStr"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>自営業等</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>4（33％）</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>8（67％）</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E63" s="13" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr"/>
+      <c r="G63" s="13" t="inlineStr"/>
+      <c r="H63" s="13" t="inlineStr"/>
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>就労していない</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>1（5％）</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>20（95％）</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E64" s="13" t="inlineStr"/>
+      <c r="F64" s="13" t="inlineStr"/>
+      <c r="G64" s="13" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr"/>
+      <c r="I64" s="13" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>10（83％）</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>2（17％）</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E65" s="13" t="inlineStr"/>
+      <c r="F65" s="13" t="inlineStr"/>
+      <c r="G65" s="13" t="inlineStr"/>
+      <c r="H65" s="13" t="inlineStr"/>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr"/>
+      <c r="G66" s="15" t="inlineStr"/>
+      <c r="H66" s="15" t="inlineStr"/>
+      <c r="I66" s="15" t="inlineStr"/>
+      <c r="J66" s="15" t="inlineStr"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>【調査対象の要件（生活の維持 × 就労継続）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="3" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>就労継続が困難</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>就労継続は該当しない</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>生活の維持が困難</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C70" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="E70" s="13" t="inlineStr"/>
+      <c r="F70" s="13" t="inlineStr"/>
+      <c r="G70" s="13" t="inlineStr"/>
+      <c r="H70" s="13" t="inlineStr"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>生活の維持は該当しない</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="C71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="E71" s="13" t="inlineStr"/>
+      <c r="F71" s="13" t="inlineStr"/>
+      <c r="G71" s="13" t="inlineStr"/>
+      <c r="H71" s="13" t="inlineStr"/>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="C72" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E72" s="15" t="inlineStr"/>
+      <c r="F72" s="15" t="inlineStr"/>
+      <c r="G72" s="15" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr"/>
+      <c r="I72" s="15" t="inlineStr"/>
+      <c r="J72" s="15" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>【より適切と思われるサービス × 提出元】</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>サービス</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>小規模多機能2事業所
+（36票）</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>他の8事業所
+（63票）</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>同一法人2事業所の占める割合</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>小規模多機能</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n">
+        <v>31</v>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>70.5％</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr"/>
+      <c r="G76" s="13" t="inlineStr"/>
+      <c r="H76" s="13" t="inlineStr"/>
+      <c r="I76" s="13" t="inlineStr"/>
+      <c r="J76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D77" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr"/>
+      <c r="G77" s="13" t="inlineStr"/>
+      <c r="H77" s="13" t="inlineStr"/>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>ｸﾞﾙｰﾌﾟﾎｰﾑ</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D78" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>25.0％</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr"/>
+      <c r="G78" s="13" t="inlineStr"/>
+      <c r="H78" s="13" t="inlineStr"/>
+      <c r="I78" s="13" t="inlineStr"/>
+      <c r="J78" s="13" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ﾎｰﾑ</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C79" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>20.0％</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="inlineStr"/>
+      <c r="G79" s="13" t="inlineStr"/>
+      <c r="H79" s="13" t="inlineStr"/>
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="13" t="inlineStr"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護､訪問入浴</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr"/>
+      <c r="G80" s="13" t="inlineStr"/>
+      <c r="H80" s="13" t="inlineStr"/>
+      <c r="I80" s="13" t="inlineStr"/>
+      <c r="J80" s="13" t="inlineStr"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>ｼｮｰﾄｽﾃｲ</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr"/>
+      <c r="G81" s="13" t="inlineStr"/>
+      <c r="H81" s="13" t="inlineStr"/>
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="13" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>通所介護､通所ﾘﾊ､認知症対応型通所</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr"/>
+      <c r="G82" s="13" t="inlineStr"/>
+      <c r="H82" s="13" t="inlineStr"/>
+      <c r="I82" s="13" t="inlineStr"/>
+      <c r="J82" s="13" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>ｻ高住</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr"/>
+      <c r="G83" s="13" t="inlineStr"/>
+      <c r="H83" s="13" t="inlineStr"/>
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="13" t="inlineStr"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>訪問看護</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr"/>
+      <c r="G84" s="13" t="inlineStr"/>
+      <c r="H84" s="13" t="inlineStr"/>
+      <c r="I84" s="13" t="inlineStr"/>
+      <c r="J84" s="13" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr"/>
+      <c r="G85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr"/>
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="13" t="inlineStr"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>居宅療養管理指導</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D86" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr"/>
+      <c r="G86" s="13" t="inlineStr"/>
+      <c r="H86" s="13" t="inlineStr"/>
+      <c r="I86" s="13" t="inlineStr"/>
+      <c r="J86" s="13" t="inlineStr"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>看護小規模多機能</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr"/>
+      <c r="G87" s="13" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr"/>
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="13" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>軽費老人ﾎｰﾑ</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr"/>
+      <c r="G88" s="13" t="inlineStr"/>
+      <c r="H88" s="13" t="inlineStr"/>
+      <c r="I88" s="13" t="inlineStr"/>
+      <c r="J88" s="13" t="inlineStr"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回ｻｰﾋﾞｽ</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr"/>
+      <c r="G89" s="13" t="inlineStr"/>
+      <c r="H89" s="13" t="inlineStr"/>
+      <c r="I89" s="13" t="inlineStr"/>
+      <c r="J89" s="13" t="inlineStr"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>訪問診療</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr"/>
+      <c r="G90" s="13" t="inlineStr"/>
+      <c r="H90" s="13" t="inlineStr"/>
+      <c r="I90" s="13" t="inlineStr"/>
+      <c r="J90" s="13" t="inlineStr"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D91" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr"/>
+      <c r="G91" s="13" t="inlineStr"/>
+      <c r="H91" s="13" t="inlineStr"/>
+      <c r="I91" s="13" t="inlineStr"/>
+      <c r="J91" s="13" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>訪問ﾘﾊ</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D92" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr"/>
+      <c r="G92" s="13" t="inlineStr"/>
+      <c r="H92" s="13" t="inlineStr"/>
+      <c r="I92" s="13" t="inlineStr"/>
+      <c r="J92" s="13" t="inlineStr"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>介護医療院</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr"/>
+      <c r="G93" s="13" t="inlineStr"/>
+      <c r="H93" s="13" t="inlineStr"/>
+      <c r="I93" s="13" t="inlineStr"/>
+      <c r="J93" s="13" t="inlineStr"/>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>0.0％</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr"/>
+      <c r="G94" s="13" t="inlineStr"/>
+      <c r="H94" s="13" t="inlineStr"/>
+      <c r="I94" s="13" t="inlineStr"/>
+      <c r="J94" s="13" t="inlineStr"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>【必要な生活支援 × 世帯類型】</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>生活支援</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>独居</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>夫婦のみ</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>単身の子と同居</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>その他の同居</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>独居の割合</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>外出同行（通院、買い物など）</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="C98" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>51.0％</t>
+        </is>
+      </c>
+      <c r="H98" s="13" t="inlineStr"/>
+      <c r="I98" s="13" t="inlineStr"/>
+      <c r="J98" s="13" t="inlineStr"/>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>見守り、声かけ</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C99" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D99" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>58.8％</t>
+        </is>
+      </c>
+      <c r="H99" s="13" t="inlineStr"/>
+      <c r="I99" s="13" t="inlineStr"/>
+      <c r="J99" s="13" t="inlineStr"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>サロンなどの定期的な通いの場</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C100" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>32.4％</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr"/>
+      <c r="I100" s="13" t="inlineStr"/>
+      <c r="J100" s="13" t="inlineStr"/>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>配食</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C101" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D101" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>62.1％</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr"/>
+      <c r="I101" s="13" t="inlineStr"/>
+      <c r="J101" s="13" t="inlineStr"/>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>掃除・洗濯</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C102" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>73.9％</t>
+        </is>
+      </c>
+      <c r="H102" s="13" t="inlineStr"/>
+      <c r="I102" s="13" t="inlineStr"/>
+      <c r="J102" s="13" t="inlineStr"/>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>調理</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C103" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>61.9％</t>
+        </is>
+      </c>
+      <c r="H103" s="13" t="inlineStr"/>
+      <c r="I103" s="13" t="inlineStr"/>
+      <c r="J103" s="13" t="inlineStr"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>買い物（宅配は含まない）</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>75.0％</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr"/>
+      <c r="I104" s="13" t="inlineStr"/>
+      <c r="J104" s="13" t="inlineStr"/>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>ゴミ出し</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C105" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>84.2％</t>
+        </is>
+      </c>
+      <c r="H105" s="13" t="inlineStr"/>
+      <c r="I105" s="13" t="inlineStr"/>
+      <c r="J105" s="13" t="inlineStr"/>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>移送サービス（介護・福祉ﾀｸｼｰ等）</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C106" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>42.1％</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr"/>
+      <c r="I106" s="13" t="inlineStr"/>
+      <c r="J106" s="13" t="inlineStr"/>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C107" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>38.5％</t>
+        </is>
+      </c>
+      <c r="H107" s="13" t="inlineStr"/>
+      <c r="I107" s="13" t="inlineStr"/>
+      <c r="J107" s="13" t="inlineStr"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>特にない</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>83.3％</t>
+        </is>
+      </c>
+      <c r="H108" s="13" t="inlineStr"/>
+      <c r="I108" s="13" t="inlineStr"/>
+      <c r="J108" s="13" t="inlineStr"/>
+    </row>
+    <row r="110" ht="104" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>注1）最も大きい差は提出元による希望の方向である。小規模多機能2事業所からの36票は86.1％が在宅サービスの追加・変更、他の8事業所からの63票は87.3％が施設等への入所・入居であり、方向が正反対である。第6章第2節の見込量で「在宅の需要」「施設等の需要」をこの99票から読む場合は、どちらの母集団を用いるかで結論が逆になる。注2）独居は45票と最も多く、うち29票（64.4％）が施設等を希望している。また介護者がいない12票のうち8票が独居である。注3）主な家族等介護者がフルタイム勤務の30票のうち20票（66.7％）が就労継続が困難に該当する。H08（就労との両立）の基準値の候補となる。注3-2）要支援・要介護度別の表の計が98票であるのは、全項目が未記入の1票（02シートNo.21）を除いているためである。注4）調査対象の要件は「生活の維持が困難」又は「家族等介護者の就労継続が困難」であり、99票の内訳は、生活の維持のみ57票、両方15票、就労継続のみ26票、要件を満たさない票は0票である。H06（在宅生活継続困難割合）の分子は72票（生活の維持が困難）となる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A110:J110"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A96:J96"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A51:J51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>② 居所変更実態調査　施設等票（18件）の調査内クロス集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>施設の種別ごとに、入所前の居場所・退去先・要介護度・医療対応力を集計する。区域内・区域外の別は調査票の「市内／市外」による（02シートNo.25）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【種別ごとの規模と回転】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>施設数</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>入所者</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>入所率</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>待機者</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>新規入所</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>退去</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>回転率</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>受入可能な医療処置
+（延べ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>152</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>57.9％</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>29.6％</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>201</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>83.8％</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>213</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>85.4％</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>92.6％</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>32.1％</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>57</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>98.3％</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>32.8％</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>121</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>95.0％</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>33.1％</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>【種別 × 入所前の居場所】（新規入所335人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>自宅</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>病院・診療所</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>自宅（区域外）</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>病院・診療所（区域外）</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等（区域外）</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>205</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="C19" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>74</v>
+      </c>
+      <c r="G19" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>335</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>【種別 × 退去先】（退去349人）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>自宅</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>病院・診療所</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>死亡</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>自宅（区域外）</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>病院・診療所（区域外）</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>他の施設・住まい等（区域外）</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>213</v>
+      </c>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="J27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>349</v>
+      </c>
+      <c r="J28" s="15" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>【種別 × 区域内・区域外】</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>入所前：区域内</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>入所前：区域外</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>区域外の割合</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>退去先：区域内</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>退去先：区域外</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>区域外の割合</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>（死亡）</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>17.8％</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>12.5％</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr"/>
+      <c r="J32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="n">
+        <v>138</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>32.7％</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>66.3％</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>84.6％</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>47.1％</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>84.2％</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>90.0％</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>60.0％</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>48.3％</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>【種別 × 入所者の要介護度】</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="inlineStr"/>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>自立</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>要支援1</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>要支援2</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>要介護1</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>要介護2</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>要介護3</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>要介護4</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>要介護5</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>特養・地域密着型特養</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>132</v>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>144</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="J45" s="15" t="n">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>【施設ごとの医療対応力と退去理由】</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>施設等の名称</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>受入可能な
+医療処置（14項目中）</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>医療処置を受けている
+入所者</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>退去理由に
+医療的ケア</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr"/>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="13" t="inlineStr"/>
+      <c r="G49" s="13" t="inlineStr"/>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>グループホームゆう</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="13" t="inlineStr"/>
+      <c r="G50" s="13" t="inlineStr"/>
+      <c r="H50" s="13" t="inlineStr"/>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>サービス付高齢者住宅ゆう</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>サ高住</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="13" t="inlineStr"/>
+      <c r="G51" s="13" t="inlineStr"/>
+      <c r="H51" s="13" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホームゆう</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="13" t="inlineStr"/>
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="13" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13" t="inlineStr"/>
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="13" t="inlineStr"/>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>老人保健施設　ひだまりの里</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="13" t="inlineStr"/>
+      <c r="G54" s="13" t="inlineStr"/>
+      <c r="H54" s="13" t="inlineStr"/>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>グループホームひばり</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="13" t="inlineStr"/>
+      <c r="G55" s="13" t="inlineStr"/>
+      <c r="H55" s="13" t="inlineStr"/>
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="13" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>介護付きホームファミリー</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="13" t="inlineStr"/>
+      <c r="G56" s="13" t="inlineStr"/>
+      <c r="H56" s="13" t="inlineStr"/>
+      <c r="I56" s="13" t="inlineStr"/>
+      <c r="J56" s="13" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法人美瑛慈光会　美瑛町老人保健施設ほの香</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>介護老人保健施設</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="13" t="inlineStr"/>
+      <c r="G57" s="13" t="inlineStr"/>
+      <c r="H57" s="13" t="inlineStr"/>
+      <c r="I57" s="13" t="inlineStr"/>
+      <c r="J57" s="13" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム東川町羽衣園</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="13" t="inlineStr"/>
+      <c r="G58" s="13" t="inlineStr"/>
+      <c r="H58" s="13" t="inlineStr"/>
+      <c r="I58" s="13" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム花時計</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="13" t="inlineStr"/>
+      <c r="G59" s="13" t="inlineStr"/>
+      <c r="H59" s="13" t="inlineStr"/>
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="13" t="inlineStr"/>
+      <c r="G60" s="13" t="inlineStr"/>
+      <c r="H60" s="13" t="inlineStr"/>
+      <c r="I60" s="13" t="inlineStr"/>
+      <c r="J60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="13" t="inlineStr"/>
+      <c r="G61" s="13" t="inlineStr"/>
+      <c r="H61" s="13" t="inlineStr"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>地域密着型特養</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="13" t="inlineStr"/>
+      <c r="G62" s="13" t="inlineStr"/>
+      <c r="H62" s="13" t="inlineStr"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="13" t="inlineStr"/>
+      <c r="G63" s="13" t="inlineStr"/>
+      <c r="H63" s="13" t="inlineStr"/>
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園サテライト特養燈</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>地域密着型特養</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="13" t="inlineStr"/>
+      <c r="G64" s="13" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr"/>
+      <c r="I64" s="13" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>株式会社健康会　グループホームひじり野</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="13" t="inlineStr"/>
+      <c r="G65" s="13" t="inlineStr"/>
+      <c r="H65" s="13" t="inlineStr"/>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム虹</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="13" t="inlineStr"/>
+      <c r="G66" s="13" t="inlineStr"/>
+      <c r="H66" s="13" t="inlineStr"/>
+      <c r="I66" s="13" t="inlineStr"/>
+      <c r="J66" s="13" t="inlineStr"/>
+    </row>
+    <row r="68" ht="104" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>注0）特別養護老人ホーム及び地域密着型特別養護老人ホームの入所者88人は、特別養護老人ホーム美瑛慈光園の入所者数が未記入である（02シートNo.11）ためであり、同施設の要介護度別の内訳58人を加えると146人・入所率96.1％となる。本表の入所率57.9％はそのままでは用いない。注1）入所前の居場所が区域外である割合は、グループホーム84.6％・特定施設84.2％・住宅型有料及びサ高住60.0％であるのに対し、特別養護老人ホーム及び地域密着型特別養護老人ホームは17.8％にとどまる。特養は区域内の高齢者を受け入れ、居住系は区域外から受け入れる構造である。第2章第3節の介護サービス自給率（δ）は区域内の高齢者が区域外の施設を利用する割合を示すが、本調査はその逆方向（区域外の高齢者が区域内の施設に入る）を示している。注2）介護老人保健施設は定員240人に対し新規入所205人・退去213人であり、回転率（新規入所÷定員）は85.4％である。在宅復帰・在宅療養支援を行う施設としての性格が数値に表れている。注3）特別養護老人ホーム及び地域密着型特別養護老人ホームは、入所前の居場所のうち「他の施設・住まい等」が23人（51.1％）で最も多い。自宅からの直接入所は10人（22.2％）である。注4）受入可能な医療処置が2項目以下の施設が4施設ある。退去理由に医療的ケアを挙げた施設と重なるかどうかは、件数が少ないため断定できない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A68:J68"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>③ 介護人材実態調査　職員個票（317人）・職員票（26人）の調査内クロス集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>施設・通所系24事業所の職員個票と、訪問系の職員票を集計する。サービス区分は事業所票の種別と施設名により受託者が付した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【資格 × 雇用形態】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1 介護福祉士</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>186（88％）</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>26（12％）</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>212</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
+      <c r="G6" s="13" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2 実務者研修修了</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>8（73％）</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>3（27％）</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>3 初任者研修修了</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>21（55％）</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>17（45％）</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>4 資格・研修なし</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>38（69％）</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>17（31％）</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
+      <c r="G10" s="15" t="inlineStr"/>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="15" t="inlineStr"/>
+      <c r="J10" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>【資格 × 年齢】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>20歳未満</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>20代</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>30代</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>40代</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>50代</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>60代</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>70代以上</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>1 介護福祉士</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>212</v>
+      </c>
+      <c r="J14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2 実務者研修修了</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3 初任者研修修了</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>4 資格・研修なし</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="J17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="J18" s="15" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>【年齢 × 雇用形態】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>20歳未満</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>9（82％）</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>2（18％）</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr"/>
+      <c r="G22" s="13" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>20代</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>61（92％）</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>5（8％）</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
+      <c r="G23" s="13" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>30代</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>50（85％）</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>9（15％）</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr"/>
+      <c r="F24" s="13" t="inlineStr"/>
+      <c r="G24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>40代</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>62（81％）</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>15（19％）</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
+      <c r="G25" s="13" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>50代</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>49（80％）</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>12（20％）</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>61</v>
+      </c>
+      <c r="E26" s="13" t="inlineStr"/>
+      <c r="F26" s="13" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>60代</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>20（56％）</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>16（44％）</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
+      <c r="G27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>70代以上</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>2（33％）</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>4（67％）</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
+      <c r="G28" s="13" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="E29" s="15" t="inlineStr"/>
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="15" t="inlineStr"/>
+      <c r="I29" s="15" t="inlineStr"/>
+      <c r="J29" s="15" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>【資格 × 勤続年数】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>1年未満</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr"/>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>1 介護福祉士</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>176（83％）</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>36（17％）</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>212</v>
+      </c>
+      <c r="E33" s="13" t="inlineStr"/>
+      <c r="F33" s="13" t="inlineStr"/>
+      <c r="G33" s="13" t="inlineStr"/>
+      <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>2 実務者研修修了</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>9（82％）</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>2（18％）</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E34" s="13" t="inlineStr"/>
+      <c r="F34" s="13" t="inlineStr"/>
+      <c r="G34" s="13" t="inlineStr"/>
+      <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>3 初任者研修修了</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>29（76％）</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>9（24％）</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="E35" s="13" t="inlineStr"/>
+      <c r="F35" s="13" t="inlineStr"/>
+      <c r="G35" s="13" t="inlineStr"/>
+      <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>4 資格・研修なし</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>39（71％）</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>16（29％）</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr"/>
+      <c r="G36" s="13" t="inlineStr"/>
+      <c r="H36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="E37" s="15" t="inlineStr"/>
+      <c r="F37" s="15" t="inlineStr"/>
+      <c r="G37" s="15" t="inlineStr"/>
+      <c r="H37" s="15" t="inlineStr"/>
+      <c r="I37" s="15" t="inlineStr"/>
+      <c r="J37" s="15" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>【勤続1年未満の直前の職場】</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>その他の介護サービス</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>介護以外の職場</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>住宅型有料・サ高住</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>初めての勤務先</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>小多機・看多機・定期巡回</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>特養・老健・医療院・ショート・GH・特定施設</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>訪問介護・入浴・夜間対応</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>通所介護・通所リハ・認知症デイ</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>1年未満</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="15" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>【サービス区分 × 資格】</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>1 介護福祉士</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>2 実務者研修修了</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>3 初任者研修修了</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>4 資格・研修なし</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>特養</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr"/>
+      <c r="H46" s="13" t="inlineStr"/>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>地密特養</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr"/>
+      <c r="H47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>老健</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr"/>
+      <c r="H48" s="13" t="inlineStr"/>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>通所リハ</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr"/>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>通所介護等</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr"/>
+      <c r="H50" s="13" t="inlineStr"/>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr"/>
+      <c r="H51" s="13" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G52" s="13" t="inlineStr"/>
+      <c r="H52" s="13" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="G53" s="13" t="inlineStr"/>
+      <c r="H53" s="13" t="inlineStr"/>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="n">
+        <v>212</v>
+      </c>
+      <c r="C54" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F54" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="G54" s="15" t="inlineStr"/>
+      <c r="H54" s="15" t="inlineStr"/>
+      <c r="I54" s="15" t="inlineStr"/>
+      <c r="J54" s="15" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>【サービス区分 × 年齢】</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>20歳未満</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>20代</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>30代</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>40代</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>50代</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>60代</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>70代以上</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>特養</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="J58" s="13" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>地密特養</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C59" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="J59" s="13" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>老健</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H60" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="J60" s="13" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>通所リハ</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="J61" s="13" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>通所介護等</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="J62" s="13" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D63" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="J63" s="13" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H64" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J64" s="13" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="J65" s="13" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F66" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="G66" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="J66" s="15" t="inlineStr"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>【サービス区分 × 雇用形態】</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="3" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
+      <c r="F69" s="3" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>特養</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>43（81％）</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>10（19％）</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="E70" s="13" t="inlineStr"/>
+      <c r="F70" s="13" t="inlineStr"/>
+      <c r="G70" s="13" t="inlineStr"/>
+      <c r="H70" s="13" t="inlineStr"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>地密特養</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>20（91％）</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>2（9％）</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E71" s="13" t="inlineStr"/>
+      <c r="F71" s="13" t="inlineStr"/>
+      <c r="G71" s="13" t="inlineStr"/>
+      <c r="H71" s="13" t="inlineStr"/>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>老健</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>71（92％）</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>6（8％）</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="E72" s="13" t="inlineStr"/>
+      <c r="F72" s="13" t="inlineStr"/>
+      <c r="G72" s="13" t="inlineStr"/>
+      <c r="H72" s="13" t="inlineStr"/>
+      <c r="I72" s="13" t="inlineStr"/>
+      <c r="J72" s="13" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>通所リハ</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>17（89％）</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>2（11％）</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E73" s="13" t="inlineStr"/>
+      <c r="F73" s="13" t="inlineStr"/>
+      <c r="G73" s="13" t="inlineStr"/>
+      <c r="H73" s="13" t="inlineStr"/>
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="13" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>通所介護等</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>14（82％）</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>3（18％）</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E74" s="13" t="inlineStr"/>
+      <c r="F74" s="13" t="inlineStr"/>
+      <c r="G74" s="13" t="inlineStr"/>
+      <c r="H74" s="13" t="inlineStr"/>
+      <c r="I74" s="13" t="inlineStr"/>
+      <c r="J74" s="13" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>58（71％）</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>24（29％）</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="E75" s="13" t="inlineStr"/>
+      <c r="F75" s="13" t="inlineStr"/>
+      <c r="G75" s="13" t="inlineStr"/>
+      <c r="H75" s="13" t="inlineStr"/>
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="13" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>特定施設</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>14（61％）</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>9（39％）</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E76" s="13" t="inlineStr"/>
+      <c r="F76" s="13" t="inlineStr"/>
+      <c r="G76" s="13" t="inlineStr"/>
+      <c r="H76" s="13" t="inlineStr"/>
+      <c r="I76" s="13" t="inlineStr"/>
+      <c r="J76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>16（70％）</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>7（30％）</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E77" s="13" t="inlineStr"/>
+      <c r="F77" s="13" t="inlineStr"/>
+      <c r="G77" s="13" t="inlineStr"/>
+      <c r="H77" s="13" t="inlineStr"/>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="C78" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="E78" s="15" t="inlineStr"/>
+      <c r="F78" s="15" t="inlineStr"/>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+      <c r="I78" s="15" t="inlineStr"/>
+      <c r="J78" s="15" t="inlineStr"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>【過去1週間の勤務時間 × 雇用形態】</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="3" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>0時間</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="13" t="inlineStr"/>
+      <c r="F82" s="13" t="inlineStr"/>
+      <c r="G82" s="13" t="inlineStr"/>
+      <c r="H82" s="13" t="inlineStr"/>
+      <c r="I82" s="13" t="inlineStr"/>
+      <c r="J82" s="13" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>20時間未満</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E83" s="13" t="inlineStr"/>
+      <c r="F83" s="13" t="inlineStr"/>
+      <c r="G83" s="13" t="inlineStr"/>
+      <c r="H83" s="13" t="inlineStr"/>
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="13" t="inlineStr"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>20〜29時間</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D84" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" s="13" t="inlineStr"/>
+      <c r="F84" s="13" t="inlineStr"/>
+      <c r="G84" s="13" t="inlineStr"/>
+      <c r="H84" s="13" t="inlineStr"/>
+      <c r="I84" s="13" t="inlineStr"/>
+      <c r="J84" s="13" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>30〜39時間</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E85" s="13" t="inlineStr"/>
+      <c r="F85" s="13" t="inlineStr"/>
+      <c r="G85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr"/>
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="13" t="inlineStr"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>40時間</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="C86" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="E86" s="13" t="inlineStr"/>
+      <c r="F86" s="13" t="inlineStr"/>
+      <c r="G86" s="13" t="inlineStr"/>
+      <c r="H86" s="13" t="inlineStr"/>
+      <c r="I86" s="13" t="inlineStr"/>
+      <c r="J86" s="13" t="inlineStr"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>40時間超</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="E87" s="13" t="inlineStr"/>
+      <c r="F87" s="13" t="inlineStr"/>
+      <c r="G87" s="13" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr"/>
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="13" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="n">
+        <v>252</v>
+      </c>
+      <c r="C88" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="D88" s="15" t="n">
+        <v>315</v>
+      </c>
+      <c r="E88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr"/>
+      <c r="G88" s="15" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr"/>
+      <c r="I88" s="15" t="inlineStr"/>
+      <c r="J88" s="15" t="inlineStr"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>【職員票（訪問系26人）の従事時間】</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>雇用形態</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>勤務時間計
+（時間）</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>1人当たり勤務時間
+（時間／週）</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>従事時間計
+（分）</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>1人当たり従事時間
+（分／週）</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>従事時間が勤務時間に
+占める割合</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>常勤</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C92" s="13" t="n">
+        <v>747</v>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>37.4</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>22142</v>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>49.4％</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr"/>
+      <c r="I92" s="13" t="inlineStr"/>
+      <c r="J92" s="13" t="inlineStr"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>非常勤</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C93" s="13" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>21.1</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>33.0％</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr"/>
+      <c r="I93" s="13" t="inlineStr"/>
+      <c r="J93" s="13" t="inlineStr"/>
+    </row>
+    <row r="95" ht="104" customHeight="1">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>注1）介護福祉士212人のうち186人（87.7％）が常勤である。一方、資格・研修なし55人のうち38人（69.1％）も常勤であり、資格の有無と雇用形態は必ずしも対応していない。注2）勤続1年未満は63人である。直前の職場は、現在の職場が初めての勤務先19人、特養・老健・介護医療院・ショートステイ・グループホーム・特定施設17人、介護以外の職場13人の順に多い。介護分野の内部での移動と他分野からの流入がいずれも一定量ある。注3）訪問系26人の従事時間は、常勤1人当たり週1,107分（18.5時間）、非常勤1人当たり週417分（6.9時間）である。勤務時間に占める従事時間の割合は常勤49.4％・非常勤33.0％であり、移動・記録・待機に相当の時間が充てられていることを示す。注4）本シートのサービス区分は、事業所票の種別（施設・居住系／通所系）と施設名により受託者が付したものである。調査票に区分の欄はない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A95:J95"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A68:J68"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>記載内容の一覧（事業所への照会用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>所在地区・区域内外・事業所名について、実際に記入された内容を提出元ごとに一覧にする。利用者票は提出元・票番号・所在地区欄の記載のみを収録し、個人の属性は一切収録していない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>【① 利用者票　所在地区欄（Q1_0）の記載　99票】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>提出元</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>記載された内容</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>票数</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ファイルと票番号</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>解釈</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>（未記入）</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>【指定居宅介護支援事業所ひばり】在宅生活改善調査_利用者票.：1〜4</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>（未記入）</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査_利用者票(1).xlsx：1・2・3</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ほたる</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1.美瑛町</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ほたる在宅生活改善調査_利用者票.xlsx：1</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>選択肢番号と町名の併記</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>回生苑居宅</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>①在宅生活改善調査_利用者票.xlsx：1／②在宅生活改善調査_利用者票.xlsx：1・2・3／③在宅生活改善調査_利用者票.xlsx：1・2／④在宅生活改善調査_利用者票.xlsx：1</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>選択肢番号のみ。1が何かは不明</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>回生苑居宅</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>④在宅生活改善調査_利用者票.xlsx：2</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>選択肢番号のみ。2が何かは不明</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>慈光園居宅</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>市街地</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査_利用者票.xlsx：1〜17</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町内の区分と推定</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>慈光園居宅</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>郊外</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査_利用者票.xlsx：13・14</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町内の区分と推定</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>（未記入）</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査【ひだまり居宅】_利用者票.xlsx：1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>東川町</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>【東川町社協】在宅生活改善調査_利用者票.xlsx：1〜11</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>町名。地区ではない</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>東神楽ケアプラン</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>コピー在宅生活改善調査_利用者票.xlsx：1・5</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>選択肢番号のみ。2が何かは不明</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>東神楽ケアプラン</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>コピー在宅生活改善調査_利用者票.xlsx：2・3・4</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>選択肢番号のみ。1が何かは不明</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町社協</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>（未記入）</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査_利用者票 (1).xlsx：1〜13</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>【七彩】在宅生活改善調査_利用者票.xlsx：1〜12／【小規模虹】在宅生活改善調査_利用者票.xlsx：1〜23</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>町名。地区ではない</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>福島県浪江町</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>【七彩】在宅生活改善調査_利用者票.xlsx：3</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>区域外の市町村名</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>（未記入）</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>【七彩】在宅生活改善調査_利用者票.xlsx：13</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr"/>
+      <c r="C21" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="D21" s="16" t="inlineStr"/>
+      <c r="E21" s="16" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="16" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>【② 施設等票　区域内・区域外（「市内／市外」）の記載　18件】</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>提出元</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>施設等の名称</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>入所前
+区域内</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>入所前
+区域外</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>入所前
+把握なし</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>退去先
+区域内</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>退去先
+区域外</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>退去先
+死亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>GHひじり野</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>株式会社健康会　グループホームひじり野</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>グループホームひばり</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>有料老人ホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ほの香</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>社会福祉法人美瑛慈光会　美瑛町老人保健施設ほの香</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>グループホームゆう</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>サービス付高齢者住宅ゆう</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>有料老人ホームゆう</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>サテライト特養　燈</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>美瑛慈光園サテライト特養燈</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>ファミリー</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>介護付きホームファミリー</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>慈光園（広域型・従来型）</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>慈光園（広域型・従来型）</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>地域密着型介護老人福祉施設美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム東川町羽衣園</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>老人保健施設　ひだまりの里</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>花時計</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホーム花時計</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>グループホーム虹</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>【③ 介護人材実態調査　事業所名の記載　27件】（所在町の欄はない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>提出元</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>記載された事業所名</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>所在町の特定</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>GHひじり野</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>グループホームひじり野</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>グループホームひばり</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>住宅型有料老人ホームひばりの森</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr"/>
+      <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>シルバーハウス訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>訪問系</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム　びえいの郷</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr"/>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>ほの香</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町老人保健施設　ほの香</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="5" t="inlineStr"/>
+      <c r="H52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>ほの香</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町老人保健施設　ほの香</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>グループホームゆう</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>サービス付高齢者住宅ゆう</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>デイサービスゆう</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホームゆう</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="5" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>サテライト特養　燈</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>美瑛慈光園サテライト特養燈</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr"/>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>ファミリー</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>介護付きホームファミリー</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="inlineStr"/>
+      <c r="H59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>介護老人保健施設回生苑</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr"/>
+      <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="5" t="inlineStr"/>
+      <c r="H61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>慈光園デイサービス</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>慈光園あるくらぶ輪</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>慈光園デイサービス</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>慈光園デイサービスセンター</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>慈光園（広域型・従来型）</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム美瑛慈光園</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>慈光園（広域型・従来型）</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr"/>
+      <c r="H65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>特別養護老人ホーム東川町羽衣園</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>老人保健施設　ひだまりの里</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>老人保健施設　ひだまりの里</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr"/>
+      <c r="H68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>花時計</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>花時計　訪問介護事業所</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>訪問系</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>華</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>有料老人ホーム華</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr"/>
+      <c r="H70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>華</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>ヘルパーステーションフラワー</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>訪問系</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>グループホーム虹</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>施設・通所系</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>調査票に欄がないため、広域連合の指定事業所台帳との突合を要する</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>【① 事業所票　利用者数の記載　15件】</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>提出元</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>ケアマネ</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>自宅等の利用者</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>サ高住等の利用者</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>居場所変更＋死亡</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>おうか</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所　おうか</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr"/>
+      <c r="H76" s="13" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>ひばり</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>指定居宅介護支援事業所ひばり</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="13" t="inlineStr"/>
+      <c r="H77" s="13" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>びえいの郷</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>シルバーハウス居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr"/>
+      <c r="H78" s="13" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>ほたる</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>小規模多機能ほたる</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" s="13" t="inlineStr"/>
+      <c r="H79" s="13" t="inlineStr"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>居宅介護支援事業所ゆう</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr"/>
+      <c r="H80" s="13" t="inlineStr"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>回生苑居宅</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>回生苑居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr"/>
+      <c r="H81" s="13" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>慈光園居宅</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>美瑛慈光園居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="G82" s="13" t="inlineStr"/>
+      <c r="H82" s="13" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>旭川福祉事業会</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>ひだまりの里居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G83" s="13" t="inlineStr"/>
+      <c r="H83" s="13" t="inlineStr"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>東川町社協</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>東川町社協居宅介護支援事業所</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G84" s="13" t="inlineStr"/>
+      <c r="H84" s="13" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>東神楽ケアプラン</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>東神楽町ケアプラン相談センター</t>
+        </is>
+      </c>
+      <c r="C85" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F85" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>東神楽包括</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>東神楽地域包括支援センター</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G86" s="13" t="inlineStr"/>
+      <c r="H86" s="13" t="inlineStr"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町包括</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>美瑛町地域包括支援センター</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町社協</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>美瑛町ケアプラン相談センター</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" s="13" t="n">
+        <v>179</v>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="G88" s="13" t="inlineStr"/>
+      <c r="H88" s="13" t="inlineStr"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能七彩</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="13" t="inlineStr"/>
+      <c r="H89" s="13" t="inlineStr"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>虹、七彩</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>美瑛慈光園小規模多機能虹</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G90" s="13" t="inlineStr"/>
+      <c r="H90" s="13" t="inlineStr"/>
+    </row>
+    <row r="92" ht="104" customHeight="1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>注1）所在地区の記載は9種類に分かれている。町名46票（美瑛町34・東川町11・「1.美瑛町」1）、「市街地」15票・「郊外」2票、選択肢番号13票（「1」10・「2」3）、未記入22票、区域外の市町村名1票である。注2）照会の際は、①地区の区分を先に定め（小学校区12地区か、市街地・郊外の2区分か）、②その区分に沿って各票の地区を記入していただく形が確実である。現在の記載のうちそのまま使えるものはない。「市街地」「郊外」の17票のみ、美瑛町内の2区分としては使える。注3）区域外の市町村名が記入された1票は、区域内の利用者であるかどうかの確認を要する。注4）事業所名が未記入の1件（慈光園従来型）は、施設等票との対応から地域密着型介護老人福祉施設美瑛慈光園と推定される。注5）本シートには利用者の属性（年齢・世帯・要介護度・回答内容）を一切収録していない。照会に必要な項目のみである。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A74:H74"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>職員数を公表データで突合できるかの検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>介護人材実態調査で把握した介護職員数を、見える化システム以外の公表データで確認できるかを検討する。見える化との突合は10シートに示している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>公表データ</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>収録されている内容</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>突合への使えるか</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>取得の方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システム
+（厚生労働省）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>指定を受けたすべての介護サービス事業所について、基本情報として従業者の職種別人数（常勤・非常勤、専従・兼務）及び常勤換算人数が公表される。事業所名・所在地・定員・利用者数も含まれる。年1回、事業所が報告する。</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>事業所単位で突合できる唯一の公表データである。調査の「介護職員数」と公表システムの「介護職員（常勤・非常勤）」を事業所ごとに対照できる。点検事項No.1（華の二重計上）・No.31（老健の乖離）・No.15〜No.19（個票の枚数との差）はいずれもこれで確認できる。</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>使える</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>同システムのオープンデータ（CSV）がサービス種別ごとに公表されている。本作業環境からは接続が制限されているため、受託者の別環境で取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス施設・事業所調査
+（厚生労働省・e-Stat）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>市区町村別の職種別従事者数（実人員・常勤換算）。見える化のM2系列の原典である。</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>市区町村単位の集計であり、事業所単位では突合できない。また保険者単位ではないため、3町の合算となる。小さい値は秘匿処理により非公表となる。見える化M2系列で既に確認しており、原典に当たっても得られる情報は増えない。</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>限定的</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>見える化M2系列で代替済み（10シート）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>北海道の指定事業所一覧
+（北海道保健福祉部）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>指定を受けた事業所の名称・所在地・サービス種別・定員。従業者数は含まれない。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>従業者数の突合には使えない。一方、点検事項No.26（事業所の所在町を記入する欄がない）の解消には使える。事業所名から所在町を特定でき、町別の集計が可能になる。</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>所在町のみ</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>北海道オープンデータポータルに「介護サービス事業所データ（位置情報付き）」がある。同じく別環境で取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="100" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>介護給付費等実態統計
+（厚生労働省）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>受給者数・給付費・サービス種別の利用状況。従事者数は含まれない。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>使えない。</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>使えない</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="100" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>広域連合の指定事業所台帳</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービスは広域連合が指定するため、事業所名・所在地・定員・人員配置基準の充足状況を保有している。居宅サービスは北海道が指定する。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>地域密着型サービス（グループホーム5・地域密着型特養3・地域密着型通所介護4・小規模多機能5）について、所在町と定員を確認できる。見える化に従事者数の系列がないサービスと重なる。</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>一部使える</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.5（指定事業所台帳）で既に依頼している。区域内事業所の所在町を追加で依頼する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>【結論と進め方】</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>結論</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>事業所単位で職員数を突合できる公表データは、介護サービス情報公表システムのみです。区域内の対象事業所は、施設・居住系18・訪問系13・通所系6・小規模多機能5・居宅介護支援10の計52事業所程度であり、手作業でも現実的な規模です。</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>これで解消できる点検事項</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項31件のうち8件が、事業所への照会を待たずに解消できます。</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>留意点</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>①公表システムの従業者数は事業所が年1回報告する値であり、報告時点が調査の令和7年4月1日と一致しない場合があります。②公表システムは職種別（介護職員・看護職員・生活相談員等）に分かれており、調査の「介護職員数」と範囲が一致するかを確認する必要があります。No.31（老健の乖離）はまさにこの範囲の問題である可能性があります。③常勤換算人数と実人員は別の値です。調査は実人員です。</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>本環境の制約</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>本作業環境は外部サイトへの接続が制限されており、介護サービス情報公表システム及び北海道オープンデータポータルへ接続できませんでした。受託者の別環境で取得し、次回の作業で突合します。</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>発注者にお願いすること</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.5（指定事業所台帳）に、区域内事業所の所在町を追加でご提供いただきたく存じます。点検事項No.26（所在町の欄がない）が解消し、町別の集計が可能になります。公表システムからの取得は受託者が行います。</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="9" t="n"/>
+    </row>
+    <row r="19" ht="104" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）本シートは公表データの所在と収録内容を整理したものであり、実際の突合は次回の作業で行う。突合の結果は10シートに追加する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -1014,7 +1014,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大3件（No.1〜No.3）の取扱いが決まってから行う。</t>
+          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大4件（No.1〜No.3・No.31）の取扱いが決まってから行う。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -10835,7 +10835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -11149,21 +11149,308 @@
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="9" t="n"/>
     </row>
-    <row r="19" ht="104" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）本シートは公表データの所在と収録内容を整理したものであり、実際の突合は次回の作業で行う。突合の結果は10シートに追加する。</t>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>【取得先】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>取得するもの</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="88" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>厚生労働省
+介護サービスの情報公表システム オープンデータ</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mhlw.go.jp/stf/kaigo-kouhyou_opendata.html</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>サービス種別ごとのCSV（ZIP圧縮・UTF-8）。事業所名・所在地・サービス種別・定員に加え、従業者数（職種別・常勤／非常勤の別、常勤換算人数）を収録する。毎年6月末時点と12月末時点の2時点が公表される。北海道分を抽出して用いる。</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>最優先</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>本作業の中心となるデータ。調査の基準日は令和7年4月1日であるため、令和6年12月末時点と令和7年6月末時点の両方を取得し、前後で挟んで確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>介護事業所・生活関連情報検索
+介護サービス情報公表システム（北海道）</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kaigokensaku.mhlw.go.jp/01/</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>個別事業所の公表画面。従業者の職種別人数、勤務形態、資格保有者数、前年度の採用者数・退職者数を収録する。</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>オープンデータCSVに載らない項目（採用者数・退職者数）を含むため、乖離のある事業所は個別画面で確認する。No.1（華）・No.31（老健3施設）はこちらで確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>北海道オープンデータポータルサイト
+介護サービス事業所データ（位置情報付き）【北海道】</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.harp.lg.jp/opendata/dataset/1739.html</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>上記①の北海道分を抽出し、緯度経度を付したCSV。所在地から事業所の所在町を特定できる。</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>点検事項No.26（人材調査に所在町の欄がない）の解消に用いる。緯度経度があるため、日常生活圏域別の配置図にも使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="88" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>北海道
+オープンデータの可視化【北海道介護サービス事業所】</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pref.hokkaido.lg.jp/kz/dxs/opendata/147354.html</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>③の解説とウェブ地図。データそのものは③と同一。</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>③の出所と更新時点の確認に用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="88" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>北海道保健福祉部高齢者保健福祉課
+介護保険サービス事業所・老人福祉施設一覧</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pref.hokkaido.lg.jp/hf/khf/jigyositei/ichiran/</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>北海道が指定する居宅サービス事業所・老人福祉施設の一覧（振興局別・Excel）。事業所名・所在地・サービス種別・定員。従業者数は含まれない。</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>上川総合振興局管内の分により、区域内事業所の網羅性（点検事項No.22・No.23の未回答事業所の特定）を確認する。住宅型有料老人ホーム・サービス付高齢者向け住宅の所在確認にも用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="88" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>北海道介護サービス情報公表センター</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.kaigojoho-hokkaido.jp/</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>北海道における公表制度の運用、公表計画、調査対象事業所の一覧。</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>公表の時点（いつ現在の値か）と、未公表・新規指定の事業所の有無を確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="88" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>e-Stat
+介護サービス施設・事業所調査</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.e-stat.go.jp/stat-search/files?tstat=000001029805</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>都道府県・市区町村別の職種別従事者数（実人員・常勤換算）。見える化M2系列の原典。</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>見える化M2系列で代替済み（10シート）。秘匿処理及び保険者単位でないことから、事業所単位の突合には使えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="88" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>e-Govデータポータル
+推奨データセット（介護サービス事業所一覧・CSV形式）</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>https://data.e-gov.go.jp/data/dataset/digi_20220315_0075</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>①のCSVが準拠する項目定義の標準例。</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>参考</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>列名と項目の意味を確認するために用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）本シートは公表データの所在と収録内容を整理したものであり、実際の突合は次回の作業で行う。突合の結果は10シートに追加する。注3）上記のURLは検索により所在を確認したものであり、本作業環境からはいずれも接続が制限されている（HTTP 403）ため、ページを開いて収録項目を直接確認したものではない。「取得するもの」の記述は制度及び公表資料の説明によるものであり、実際の列構成は取得後に確認する。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -783,12 +783,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>4件</t>
+          <t>5件</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと、④介護老人保健施設・通所リハビリテーションの介護職員数が見える化システムの従事者数と一致しないこと。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
+          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと、④介護老人保健施設・通所リハビリテーションの介護職員数が見える化システムの従事者数と一致しないこと、⑤区域内最大の特定施設（さわやか東神楽館・定員100人）が居所変更実態調査に回答しておらず、特定施設の区域内定員が58人ではなく156人であること。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
@@ -1014,7 +1014,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大4件（No.1〜No.3・No.31）の取扱いが決まってから行う。</t>
+          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大5件（No.1〜No.3・No.31・No.32）の取扱いが決まってから行う。</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホーム3施設・サービス付高齢者向け住宅1施設の定員121人・入居者115人を掲載する。これらは介護保険の指定サービスではないため見える化に現れず、今回の調査が唯一の把握手段である（10シート）。</t>
+          <t>北海道の名簿（令和8年7月1日現在）により、住宅型有料老人ホーム9施設・定員223人、サービス付き高齢者向け住宅2件・66戸、軽費老人ホーム1施設・50人を掲載する。これらは介護保険の指定サービスではないため見える化に現れない。定員は名簿、入居者数は調査による（住まいと施設の公表名簿との突合 04シート）。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>No.30（有料老人ホーム華の施設等票）の提出の有無。提出があれば定員・入居者数が増える。</t>
+          <t>入居者数は調査に回答した4施設分（115人）しか把握できていない。定員のみの掲載とするか、入居者数を照会するかを決める。</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1284,9 +1284,9 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>着手可</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
     <row r="15" ht="104" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>注1）No.9（医療と介護の連携）のみ、点検で見つかった事項の影響を受けずに着手できる。残る8件は重大4件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
+          <t>注1）No.8（住まいの供給量）とNo.9（医療と介護の連携）は、点検で見つかった事項の影響を受けずに着手できる。No.8は北海道の名簿により定員を確定できるようになったため、確認待ちから着手可に改めた。残る7件は重大5件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2127,49 +2127,78 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>住宅型有料老人ホーム・サ高住</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="n">
+          <t>住宅型有料老人ホーム・サ高住・軽費</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
+      <c r="D31" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>33％</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>見える化に事業所数の系列がない。受領した4施設の定員は31＋30＋30＋30＝121人である。介護人材実態調査には有料老人ホーム華からも回答があるが、居所変更実態調査の施設等票は受領していない（No.30）。</t>
+          <t>見える化に事業所数の系列がない。北海道の名簿により、区域内には住宅型有料9施設223人・サービス付き高齢者向け住宅2件66戸・軽費老人ホーム1施設50人がある。調査に回答したのは4施設・定員121人にとどまる（No.30）。</t>
         </is>
       </c>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="9" t="n"/>
     </row>
-    <row r="33" ht="104" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>注1）見える化のK系列は各年度の10月1日現在、M2系列は介護サービス施設・事業所調査（各年10月1日現在）による。今回の3調査は令和7年4月1日現在であり、半年のずれがある。注2）M2系列の従事者数は職種別の実人員である。本表では「介護職員」の実数を用いた。認定者1万対の系列は用いていない。注3）特養・地域密着型特養の差は未回答1施設ずつで説明できるのに対し、老健・通所リハは全施設が回答したうえで差が生じている。この2サービスは、調査での「介護職員」の範囲の解釈を確認する。注4）住宅型有料老人ホーム・サービス付高齢者向け住宅は介護保険の指定サービスではないため見える化に現れない。今回の居所変更実態調査で定員121人・入居者115人を把握したことは、第2章第3節の住まいの供給量の記述を初めて可能にするものである。</t>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>特定施設入居者生活介護（介護付有料）</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>見える化K2a（3事業所）と北海道の届出済有料老人ホーム一覧が一致する。定員は156人である。調査に回答したのは2施設（58人）で、さわやか東神楽館（100人）が回答していない（No.32）。</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="9" t="n"/>
+    </row>
+    <row r="34" ht="104" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>注1）見える化のK系列は各年度の10月1日現在、M2系列は介護サービス施設・事業所調査（各年10月1日現在）による。今回の3調査は令和7年4月1日現在であり、半年のずれがある。注2）M2系列の従事者数は職種別の実人員である。本表では「介護職員」の実数を用いた。認定者1万対の系列は用いていない。注3）特養・地域密着型特養の差は未回答1施設ずつで説明できるのに対し、老健・通所リハは全施設が回答したうえで差が生じている。この2サービスは、調査での「介護職員」の範囲の解釈を確認する。注4）住宅型有料老人ホーム・サービス付高齢者向け住宅・軽費老人ホームは介護保険の指定サービスではないため見える化に現れない。令和8年8月4日に受領した北海道の名簿により、区域内には12施設・定員339人（戸）があることが確認された。調査で把握できたのは4施設・121人にとどまる。定員は名簿により、入居者数は調査によることとなる（住まいと施設の公表名簿との突合）。注5）本表は令和8年8月4日に北海道の名簿を受領した結果を反映している。K系列との突合により、特定施設は1施設、特養・地域密着型特養は各1施設が調査に回答していないことが確定した。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="F28:H28"/>
+    <mergeCell ref="A34:H34"/>
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="F27:H27"/>
     <mergeCell ref="D19:H19"/>
+    <mergeCell ref="F32:H32"/>
     <mergeCell ref="F26:H26"/>
-    <mergeCell ref="A33:H33"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="F29:H29"/>
@@ -11093,7 +11122,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項31件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項32件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -12065,7 +12094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12079,7 +12108,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>点検で見つかった事項（31件）</t>
+          <t>点検で見つかった事項（32件）</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13037,17 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>有料老人ホーム華の施設等票</t>
+          <t>介護保険外の住まいの施設等票の未提出</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査には有料老人ホーム華から事業所票が提出されているが、居所変更実態調査の施設等票は受領した18件に含まれていない。他の住宅型有料老人ホーム3施設（ひばりの森・びえいの郷・花時計）はいずれも提出している。</t>
+          <t>北海道の届出済有料老人ホーム一覧（令和8年7月1日現在）により、区域内の住宅型有料老人ホームは9施設・定員223人であることが確認された。居所変更実態調査に回答したのはひばりの森・びえいの郷・花時計の3施設で、華（定員31人）・ひがしかぐらふらわーはうす（18人）・縁結び（22人）・わくらば（6人）・わくらばⅡ（18人）・恩送り（25人）の6施設が回答していない。サービス付き高齢者向け住宅も桜華（36戸）、軽費老人ホームもケアハウスびえい（50人）が回答していない。</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>提出対象であったかどうかを確認する。対象であれば、住宅型有料老人ホームの定員・入居者数（現在121人・115人）と入退去の把握が1施設分不足する。</t>
+          <t>配布対象であったかどうかを確認する。定員は名簿により確定できるが、入居者数は名簿になく、把握できるのは調査に回答した4施設分のみである（住まいと施設の公表名簿との突合 04・05シート）。</t>
         </is>
       </c>
     </row>
@@ -13052,17 +13081,47 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="104" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大4件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認19件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
+    <row r="36" ht="90" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>特定施設の1施設が回答していない</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>北海道の届出済有料老人ホーム一覧により、区域内の介護付有料老人ホーム（特定施設入居者生活介護の指定あり）は3施設・定員156人であることが確認された。見える化K2a（3事業所）と一致する。居所変更実態調査に回答したのは高齢者ふれあいハウスファミリー（36人）とゆう（20人）の2施設で、さわやか東神楽館（東神楽町・定員100人）が回答していない。</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>区域内最大の特定施設が抜けているため、特定施設の入所前の居場所・退去先の集計（新規入所の84.2％が区域外）は定員56人分に基づくものである。配布したが回収できなかったのか、配布先から漏れていたのかを確認する（住まいと施設の公表名簿との突合 05シート）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="104" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大5件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認19件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -10933,22 +10933,23 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>指定を受けたすべての介護サービス事業所について、基本情報として従業者の職種別人数（常勤・非常勤、専従・兼務）及び常勤換算人数が公表される。事業所名・所在地・定員・利用者数も含まれる。年1回、事業所が報告する。</t>
+          <t>指定を受けたすべての介護サービス事業所について、個別事業所の公表画面には、従業者の職種別人数（常勤・非常勤、専従・兼務）及び常勤換算人数、前年度の採用者数・退職者数が掲載される。年1回、事業所が報告する。【重要】オープンデータのCSVには従業者数は含まれない。令和8年8月4日に受領したCSVで確認したところ、収録されているのは事業所名・所在地・緯度経度・法人名・事業所番号・利用可能曜日・定員・URL等であり、従業者数の列はない。定員の列も大半が0又は空欄である。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>事業所単位で突合できる唯一の公表データである。調査の「介護職員数」と公表システムの「介護職員（常勤・非常勤）」を事業所ごとに対照できる。点検事項No.1（華の二重計上）・No.31（老健の乖離）・No.15〜No.19（個票の枚数との差）はいずれもこれで確認できる。</t>
+          <t>事業所単位で職員数を突合できる唯一の公表データであるが、オープンデータでは突合できず、個別事業所の公表画面を1件ずつ開く必要がある。点検事項No.1（華の二重計上）・No.31（老健の乖離）・No.15〜No.19（個票の枚数との差）はいずれもこれで確認できる。</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>使える</t>
+          <t>使える
+（個別画面）</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>同システムのオープンデータ（CSV）がサービス種別ごとに公表されている。本作業環境からは接続が制限されているため、受託者の別環境で取得する。</t>
+          <t>区域内の対象事業所は52事業所程度であり、個別画面を開く作業は現実的な規模である。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
     </row>
@@ -10990,27 +10991,27 @@
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>北海道の指定事業所一覧
-（北海道保健福祉部）</t>
+（北海道保健福祉部）【令和8年8月4日受領済】</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>指定を受けた事業所の名称・所在地・サービス種別・定員。従業者数は含まれない。</t>
+          <t>指定を受けた事業所の名称・所在地・法人名・事業所番号、及び運営規程に定める「通常の事業実施地域」。サービス種別ごとに47区分のシートに分かれる。従業者数・定員は含まれない。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>従業者数の突合には使えない。一方、点検事項No.26（事業所の所在町を記入する欄がない）の解消には使える。事業所名から所在町を特定でき、町別の集計が可能になる。</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>所在町のみ</t>
+          <t>従業者数の突合には使えない。一方、点検事項No.26（事業所の所在町を記入する欄がない）はこれで解消した。区域内の指定事業所124件を抽出し、13区分のうち10区分で見える化K系列の事業所数と一致することを確認した（住まいと施設の公表名簿との突合 07シート）。訪問介護13事業所という母数が確定し、点検事項No.23（訪問系の回収状況）の評価ができるようになった。</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>所在町は解消</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北海道オープンデータポータルに「介護サービス事業所データ（位置情報付き）」がある。同じく別環境で取得する。</t>
+          <t>受領済。あわせて北海道オープンデータポータルの「介護サービス事業所データ（位置情報付き）」も受領した。緯度経度により圏域別の配置図を作成できる</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11107,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>事業所単位で職員数を突合できる公表データは、介護サービス情報公表システムのみです。区域内の対象事業所は、施設・居住系18・訪問系13・通所系6・小規模多機能5・居宅介護支援10の計52事業所程度であり、手作業でも現実的な規模です。</t>
+          <t>事業所単位で職員数を突合できる公表データは、介護サービス情報公表システムの個別事業所の公表画面のみです。令和8年8月4日にオープンデータのCSVを受領して確認したところ、CSVには従業者数の列がありませんでした。前回「オープンデータで突合できる」とお示ししたのは誤りで、個別画面を1件ずつ開く必要があります。区域内の対象事業所は、施設・居住系20・訪問系13・通所系6・小規模多機能5・居宅介護支援13の計57事業所程度であり、手作業でも現実的な規模です。</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -11149,12 +11150,12 @@
     <row r="16" ht="76" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>本環境の制約</t>
+          <t>受領の状況</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>本作業環境は外部サイトへの接続が制限されており、介護サービス情報公表システム及び北海道オープンデータポータルへ接続できませんでした。受託者の別環境で取得し、次回の作業で突合します。</t>
+          <t>令和8年8月4日に、北海道オープンデータポータルの「介護サービス事業所データ（位置情報付き）」、介護サービス情報公表システムのオープンデータ（訪問介護・訪問入浴介護・訪問看護の3区分）、北海道の介護保険事業所一覧（47区分）を受領しました。事業所数・所在町・実施地域の突合は完了しています（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数であり、個別事業所の公表画面によります。本作業環境からは接続が制限されているため、受託者の別環境で行います。</t>
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
@@ -11467,7 +11468,7 @@
     <row r="30" ht="104" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）本シートは公表データの所在と収録内容を整理したものであり、実際の突合は次回の作業で行う。突合の結果は10シートに追加する。注3）上記のURLは検索により所在を確認したものであり、本作業環境からはいずれも接続が制限されている（HTTP 403）ため、ページを開いて収録項目を直接確認したものではない。「取得するもの」の記述は制度及び公表資料の説明によるものであり、実際の列構成は取得後に確認する。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
+          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）事業所数・所在町・通常の事業実施地域の突合は令和8年8月4日の受領により完了した（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数の突合である。注3）上記のうち①のCSVについては、受領前に「従業者数（職種別・常勤換算）を収録する」と記載していたが、実際に受領したCSVには従業者数の列がなかった。検索により得た説明を確認せずに記載したことによる誤りであり、訂正した。従業者数は個別事業所の公表画面による。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11468,7 +11468,7 @@
     <row r="30" ht="104" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）事業所数・所在町・通常の事業実施地域の突合は令和8年8月4日の受領により完了した（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数の突合である。注3）上記のうち①のCSVについては、受領前に「従業者数（職種別・常勤換算）を収録する」と記載していたが、実際に受領したCSVには従業者数の列がなかった。検索により得た説明を確認せずに記載したことによる誤りであり、訂正した。従業者数は個別事業所の公表画面による。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
+          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）令和8年8月5日に、グループホームファミリーの個別公表画面を受領した。総従業者数15人・介護職員常勤12人・介護職員の退職者数2人・経験年数5年以上の割合41.7％を確認でき、本方法により職員数を突合できることが実証された（住まいと施設の公表名簿との突合 10シート）。一方、グループホームくるみの郷は公表システムに掲載がなく、この方法では把握できない。同事業所は地域密着型サービスであり指定権者が発注者であるため、資料依頼No.5（指定事業所台帳）による。事業所数・所在町・通常の事業実施地域の突合は令和8年8月4日の受領により完了した（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数の突合である。注3）上記のうち①のCSVについては、受領前に「従業者数（職種別・常勤換算）を収録する」と記載していたが、実際に受領したCSVには従業者数の列がなかった。検索により得た説明を確認せずに記載したことによる誤りであり、訂正した。従業者数は個別事業所の公表画面による。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>区域内最大の特定施設が抜けているため、特定施設の入所前の居場所・退去先の集計（新規入所の84.2％が区域外）は定員56人分に基づくものである。配布したが回収できなかったのか、配布先から漏れていたのかを確認する（住まいと施設の公表名簿との突合 05シート）。</t>
+          <t>区域内最大の特定施設が抜けているため、特定施設の入所前の居場所・退去先の集計（新規入所の84.2％が区域外）は定員56人分に基づくものである。令和8年8月5日に同施設の公表画面（記入日 令和7年10月6日）を受領し、定員100人・入居者97人・要介護度別の内訳・介護職員31人・昨年度の退居者22人を確認した。供給量と職員数は補えたが、入所前の居場所と退去先は公表されていないため補えない。配布したが回収できなかったのか、配布先から漏れていたのかを確認する（住まいと施設の公表名簿との突合 05・10シート）。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>19件</t>
+          <t>20件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項32件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項33件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -12095,7 +12095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12109,7 +12109,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>点検で見つかった事項（32件）</t>
+          <t>点検で見つかった事項（33件）</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。</t>
+          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。</t>
         </is>
       </c>
     </row>
@@ -13112,17 +13112,47 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="104" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大5件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認19件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
+    <row r="37" ht="90" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>③人材</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>グループホームびえいの郷の常勤・非常勤の内訳</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>事業所票に介護職員16人・常勤10人と記入され、非常勤の欄が未記入である。常勤と非常勤の合計10人が介護職員数16人と一致しない（差6人）。施設・通所系24事業所の合計でも、介護職員319人に対し常勤258人・非常勤55人（計313人）で6人の差が生じている。</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月5日に受領した同事業所の公表画面（記入日 令和7年10月4日）では、介護職員は常勤10人・非常勤7人である。常勤10人は調査と一致し、未記入の非常勤は6人程度とみられる。常勤・非常勤の割合を計画本文に用いる場合は、記入のあった313人を分母とする旨を明記する。実数は事業所への照会により確定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="104" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大5件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認20件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -783,12 +783,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>5件</t>
+          <t>6件</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと、④介護老人保健施設・通所リハビリテーションの介護職員数が見える化システムの従事者数と一致しないこと、⑤区域内最大の特定施設（さわやか東神楽館・定員100人）が居所変更実態調査に回答しておらず、特定施設の区域内定員が58人ではなく156人であること。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
+          <t>①同一法人による職員数の二重計上（13人）、②同一法人の小規模多機能2事業所が利用者票の70.5％を占め「小規模多機能がより適切」という回答に偏っていること、③所在地区の記入形式が統一されておらず地区別集計ができないこと、④介護老人保健施設・通所リハビリテーションの介護職員数が見える化システムの従事者数と一致しないこと、⑤区域内最大の特定施設（さわやか東神楽館・定員100人）が居所変更実態調査に回答しておらず、特定施設の区域内定員が58人ではなく156人であること、⑥居所変更実態調査の対象が26施設ではなく31施設であり、未回答が9施設ではなく13施設（把握率58.1％）であること。いずれも集計方法を決めないと計画本文の数値が変わります。</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
@@ -1014,7 +1014,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大5件（No.1〜No.3・No.31・No.32）の取扱いが決まってから行う。</t>
+          <t>点検で見つかった事項の取扱いを決めたうえで、計画素案のどの箇所に反映するかを整理する。反映は、重大6件（No.1〜No.3・No.31・No.32）の取扱いが決まってから行う。</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
     <row r="15" ht="104" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>注1）No.8（住まいの供給量）とNo.9（医療と介護の連携）は、点検で見つかった事項の影響を受けずに着手できる。No.8は北海道の名簿により定員を確定できるようになったため、確認待ちから着手可に改めた。残る7件は重大5件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
+          <t>注1）No.8（住まいの供給量）とNo.9（医療と介護の連携）は、点検で見つかった事項の影響を受けずに着手できる。No.8は北海道の名簿により定員を確定できるようになったため、確認待ちから着手可に改めた。残る7件は重大6件又は要確認の解消を待つ。注2）本シートの反映方針は受託者の案であり、仕様書の定めにより業務工程の都度発注者のご意向を確認する。特にNo.2（「市内／市外」の定義）とNo.6（小規模多機能の偏りの取扱い）は、計画本文の数値が変わるため、ご意向を確認したうえで反映する。注3）事業所への照会を行う場合の照会先・照会方法・期限は、発注者と協議のうえ定める。受託者が直接照会するか、広域連合を通じるかを確認する。</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項33件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項34件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -12095,7 +12095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12109,7 +12109,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>点検で見つかった事項（33件）</t>
+          <t>点検で見つかった事項（34件）</t>
         </is>
       </c>
     </row>
@@ -13142,17 +13142,47 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="104" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大5件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認20件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
+    <row r="38" ht="90" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>居所変更実態調査の対象と未回答の施設数</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>報告書及び管理表で「区域内の施設・住まい26施設・未回答9施設」と記述していたが、26－18＝8であり算術的に成り立たない。北海道の名簿により区域内の施設・住まいを数え直すと、介護保険の指定を受ける施設・居住系19（特養3・地域密着型特養3・老健3・グループホーム7・特定施設3）と、指定を受けない住まい12（住宅型有料9・サービス付き高齢者向け住宅2・軽費老人ホーム1）の計31施設である。回答は18施設（指定14・指定外4）、未回答は13施設（指定5・指定外8）で、把握率は58.1％である。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>「26施設・未回答9施設」は、アゼリアハイツ（広域型・ユニット型）及びグループホーム2事業所を未回答として数えていなかったことによる誤りである。令和8年8月5日に31施設・回答18・未回答13へ訂正した。対象・回答・未回答の施設名は住まいと施設の公表名簿との突合05シートに固定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="104" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大6件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認20件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>21件</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -12095,7 +12095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12104,12 +12104,15 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>点検で見つかった事項（34件）</t>
+          <t>点検で見つかった事項（35件）</t>
         </is>
       </c>
     </row>
@@ -12149,6 +12152,21 @@
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>取扱い・確認すること</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>確認主体</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>確認の期限</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>反映先（計画素案）</t>
         </is>
       </c>
     </row>
@@ -12181,6 +12199,21 @@
           <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。</t>
         </is>
       </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -12211,6 +12244,21 @@
           <t>回答者が自らのサービス種別を推奨する構造になっているため、44件をそのまま小規模多機能の需要として第6章第2節の見込量に用いると過大となる。提出元を除いた集計（13件）を併記し、本文には「回答事業所の構成による偏りがある」旨を明記する。</t>
         </is>
       </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -12241,6 +12289,21 @@
           <t>地区別・日常生活圏域別の集計ができない。第1章第7節（日常生活圏域）及び第2章の地域分析に用いられない。地区の定義（小学校区か市街地・郊外か）を定めたうえで、事業所に再照会するか、地区別の分析を行わないかを決める。</t>
         </is>
       </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>発注者（利用者票の所在地区の記入形式）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>第1章第7節</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -12271,6 +12334,21 @@
           <t>Q1-2の記入漏れと考えられる。利用者数を確認する。第2章の在宅利用者に対する割合の分母となる。</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -12301,6 +12379,21 @@
           <t>Q1-2とQ1-3のいずれかの記入漏れ又は取り違えと考えられる。確認する。</t>
         </is>
       </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -12331,6 +12424,21 @@
           <t>利用者数と居場所変更者数を確認する。</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -12361,6 +12469,21 @@
           <t>事業所の休止・廃止か、記入漏れかを確認する。休止・廃止であれば第2章第3節の事業所数に影響する。</t>
         </is>
       </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -12391,6 +12514,21 @@
           <t>居場所変更が0件であるのか未記入であるのかを確認する。0件であれば0と記入していただく。</t>
         </is>
       </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -12421,6 +12559,21 @@
           <t>いずれかの記入誤りである。第2章第3節の施設利用者数に影響する。</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -12451,6 +12604,21 @@
           <t>同上。</t>
         </is>
       </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -12481,6 +12649,21 @@
           <t>入所者数を確認する。58人であれば入所率96.7％となる。</t>
         </is>
       </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="90" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -12511,6 +12694,21 @@
           <t>定員又は入居者数の記入誤りか、定員に含まれない区分の入居者を含めたかを確認する。</t>
         </is>
       </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="90" customHeight="1">
       <c r="A17" s="4" t="n">
@@ -12541,6 +12739,21 @@
           <t>同一法人の2施設で同一の待機者名簿を計上している可能性が高い。単純に合計すると110人となり過大となる。重複を除いた実数を確認する。第6章第4節（施設整備の方針）の根拠となる数値である。</t>
         </is>
       </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>発注者（特別養護老人ホームの入所申込者名簿）</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="90" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -12571,6 +12784,21 @@
           <t>退去者0件であれば合計欄に0と記入していただく。</t>
         </is>
       </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -12601,6 +12829,21 @@
           <t>介護職員数と職員個票のいずれが正しいかを確認する。職員個票は資格・年齢・勤続年数の分析に用いるため、枚数と介護職員数を一致させる。</t>
         </is>
       </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="90" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -12631,6 +12874,21 @@
           <t>同上。</t>
         </is>
       </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="90" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -12661,6 +12919,21 @@
           <t>同上。</t>
         </is>
       </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="90" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -12691,6 +12964,21 @@
           <t>訪問系は職員1人につき1ファイルの提出を求めている。3人分が未提出であるか、対象外の職員がいるかを確認する。</t>
         </is>
       </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -12721,6 +13009,21 @@
           <t>No.1の重複の疑いと合わせて確認する。施設・通所系の職員個票13人分と同一の職員である可能性がある。</t>
         </is>
       </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="90" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -12751,6 +13054,21 @@
           <t>事業所名を確認する。</t>
         </is>
       </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="90" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -12781,6 +13099,21 @@
           <t>白紙の1票は集計から除く。エラー表示の1件は回答を確認する。Q3-1の未記入は、集計の分母を回答票数とすることを明記する。</t>
         </is>
       </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="90" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -12811,6 +13144,21 @@
           <t>3事業所の介護職員が集計に含まれていない。提出の有無を確認する。第3章第5節（人材）の従事者数に影響する。</t>
         </is>
       </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>第3章第5節</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="90" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -12841,6 +13189,21 @@
           <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。13事業所との差が未回収であるのか、区域外の事業所を含む数であるのかを確認する。</t>
         </is>
       </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="90" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -12871,6 +13234,21 @@
           <t>提出対象としたかどうかを確認する。</t>
         </is>
       </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="90" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -12901,6 +13279,21 @@
           <t>「市内」が当該施設の所在する町内を指すのか、広域連合の区域内（3町）を指すのかで、区域内198人・区域外137人という区分の意味が変わる。第2章第3節の介護サービス自給率（δ）は市区町村単位の指標であるため、町単位で読む場合は自給率と接続できる。定義を確認する。</t>
         </is>
       </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="90" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -12931,6 +13324,21 @@
           <t>町別の集計は事業所名からの推定によることになる。第2章の町別分析及び第5章の3町の役割分担に用いる場合は、広域連合が保有する事業所台帳との突合を要する。</t>
         </is>
       </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="90" customHeight="1">
       <c r="A31" s="4" t="n">
@@ -12961,6 +13369,21 @@
           <t>集計値そのものに誤りはないが、報告書で設問番号により参照する際に取り違えるおそれがある。図表の注記では設問文で示す。</t>
         </is>
       </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="90" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -12991,6 +13414,21 @@
           <t>調査結果を計画本文に用いる際は「令和7年4月1日現在」又は「令和6年度」と時点を明記し、令和7年度の実績（認定者数1,984人等）と混同しないようにする。</t>
         </is>
       </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="90" customHeight="1">
       <c r="A33" s="4" t="n">
@@ -13021,6 +13459,21 @@
           <t>施設単位の介護職員数が、その施設の入居者に提供される介護の量を表さない。第3章第5節で施設種別ごとの職員配置を記述する際は、住まいと介護サービスの提供主体が別であることを注記する。</t>
         </is>
       </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>受託者（記録）・発注者（次期様式）</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>第11期計画の調査設計時</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>第3章第5節</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="90" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -13051,6 +13504,21 @@
           <t>配布対象であったかどうかを確認する。定員は名簿により確定できるが、入居者数は名簿になく、把握できるのは調査に回答した4施設分のみである（住まいと施設の公表名簿との突合 04・05シート）。</t>
         </is>
       </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="90" customHeight="1">
       <c r="A35" s="4" t="n">
@@ -13081,6 +13549,21 @@
           <t>①調査で「介護職員」に支援相談員・その他の職員を含めて記入したのか、②見える化の令和5・6年度の値が実態より低いのかを確認する。第3章第5節では「介護老人福祉施設の従事者数は平成29年度116人から令和6年度105人へ9.5％減少」と記述しており、老健の従事者数の推移を同じ枠組みで記述できるかどうかが変わる。調査票の職種の範囲を事業所に照会する。</t>
         </is>
       </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>第3章第5節</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="90" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -13111,6 +13594,21 @@
           <t>区域内最大の特定施設が抜けているため、特定施設の入所前の居場所・退去先の集計（新規入所の84.2％が区域外）は定員56人分に基づくものである。令和8年8月5日に同施設の公表画面（記入日 令和7年10月6日）を受領し、定員100人・入居者97人・要介護度別の内訳・介護職員31人・昨年度の退居者22人を確認した。供給量と職員数は補えたが、入所前の居場所と退去先は公表されていないため補えない。配布したが回収できなかったのか、配布先から漏れていたのかを確認する（住まいと施設の公表名簿との突合 05・10シート）。</t>
         </is>
       </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>発注者（さわやか東神楽館への照会）</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="90" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -13141,6 +13639,21 @@
           <t>令和8年8月5日に受領した同事業所の公表画面（記入日 令和7年10月4日）では、介護職員は常勤10人・非常勤7人である。常勤10人は調査と一致し、未記入の非常勤は6人程度とみられる。常勤・非常勤の割合を計画本文に用いる場合は、記入のあった313人を分母とする旨を明記する。実数は事業所への照会により確定する。</t>
         </is>
       </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>提出元の事業所（発注者を経由）</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="90" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -13171,18 +13684,78 @@
           <t>「26施設・未回答9施設」は、アゼリアハイツ（広域型・ユニット型）及びグループホーム2事業所を未回答として数えていなかったことによる誤りである。令和8年8月5日に31施設・回答18・未回答13へ訂正した。対象・回答・未回答の施設名は住まいと施設の公表名簿との突合05シートに固定する。</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="104" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>注1）重大6件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認20件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。</t>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>受託者（北海道の名簿による区域内母数の確定）</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>素案の確定前</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>②居所</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>グループホームくるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護7事業所のうち、グループホームくるみの郷のみ介護サービス情報公表システムに掲載がなく、定員を公表資料で確認できない。このため、区域内の認知症対応型共同生活介護の定員99人及び介護保険の指定を受ける施設・居住系の区域内定員717人は同事業所を含まない値である。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>定員ベースの把握率74.1％（717人中531人）は暫定値である。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合であることから、資料依頼No.5（指定事業所台帳）により定員をご提供いただく。受領後に第2章第3節の定員及び第7章第1節の把握率を更新する。</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>発注者（指定事業所台帳・資料依頼No.5）</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>ヒアリング（項目4・6）の時点</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節、第7章第1節</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="104" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>注1）重大6件は、集計の方法を決めないと計画本文に載せる数値が変わるものである。No.1は介護職員の総数、No.2は小規模多機能の見込量、No.3は地区別分析の可否、No.31は従事者数の推移の記述に直結する。注2）要確認21件は、事業所への照会により解消できる見込みである。照会の要否と方法は発注者のご意向を確認する。注3）様式・網羅性8件は、今回の調査票が第9期の様式を踏襲していることによるものであり、今回の集計を止めるものではない。第11期以降の様式の見直しの材料として記録する。注4）確認主体・確認の期限は重要度による既定値であり、個別に定めるものは上書きしている。反映先は取扱い欄に記載した計画素案の章節を機械的に抽出したものである。本シートが未確定事項の内部管理版であり、「実施済み調査 結果報告書」（Word）の未確定事項表は本シートを要約したものである。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11072,7 +11072,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.5（指定事業所台帳）で既に依頼している。区域内事業所の所在町を追加で依頼する。</t>
+          <t>資料依頼No.18（指定事業所台帳）で既に依頼している。区域内事業所の所在町を追加で依頼する。</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項34件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.5（指定事業所台帳）に、区域内事業所の所在町を追加でご提供いただきたく存じます。点検事項No.26（所在町の欄がない）が解消し、町別の集計が可能になります。公表システムからの取得は受託者が行います。</t>
+          <t>資料依頼No.18（指定事業所台帳）に、区域内事業所の所在町を追加でご提供いただきたく存じます。点検事項No.26（所在町の欄がない）が解消し、町別の集計が可能になります。公表システムからの取得は受託者が行います。</t>
         </is>
       </c>
       <c r="C17" s="8" t="n"/>
@@ -11468,7 +11468,7 @@
     <row r="30" ht="104" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）令和8年8月5日に、グループホームファミリーの個別公表画面を受領した。総従業者数15人・介護職員常勤12人・介護職員の退職者数2人・経験年数5年以上の割合41.7％を確認でき、本方法により職員数を突合できることが実証された（住まいと施設の公表名簿との突合 10シート）。一方、グループホームくるみの郷は公表システムに掲載がなく、この方法では把握できない。同事業所は地域密着型サービスであり指定権者が発注者であるため、資料依頼No.5（指定事業所台帳）による。事業所数・所在町・通常の事業実施地域の突合は令和8年8月4日の受領により完了した（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数の突合である。注3）上記のうち①のCSVについては、受領前に「従業者数（職種別・常勤換算）を収録する」と記載していたが、実際に受領したCSVには従業者数の列がなかった。検索により得た説明を確認せずに記載したことによる誤りであり、訂正した。従業者数は個別事業所の公表画面による。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.5（指定事業所台帳）への所在町の追加のみである。</t>
+          <t>注1）介護サービス情報公表システムは介護保険法第115条の35に基づく制度であり、指定事業者に情報の報告が義務付けられている。調査に回答していない事業所についても情報が得られる点が大きい。注2）令和8年8月5日に、グループホームファミリーの個別公表画面を受領した。総従業者数15人・介護職員常勤12人・介護職員の退職者数2人・経験年数5年以上の割合41.7％を確認でき、本方法により職員数を突合できることが実証された（住まいと施設の公表名簿との突合 10シート）。一方、グループホームくるみの郷は公表システムに掲載がなく、この方法では把握できない。同事業所は地域密着型サービスであり指定権者が発注者であるため、資料依頼No.18（指定事業所台帳）による。事業所数・所在町・通常の事業実施地域の突合は令和8年8月4日の受領により完了した（住まいと施設の公表名簿との突合 07・08シート）。残るのは従業者数の突合である。注3）上記のうち①のCSVについては、受領前に「従業者数（職種別・常勤換算）を収録する」と記載していたが、実際に受領したCSVには従業者数の列がなかった。検索により得た説明を確認せずに記載したことによる誤りであり、訂正した。従業者数は個別事業所の公表画面による。注4）取得は受託者が行うものであり、発注者にお願いするのは資料依頼No.18（指定事業所台帳）への所在町の追加のみである。</t>
         </is>
       </c>
     </row>
@@ -13726,12 +13726,12 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>定員ベースの把握率74.1％（717人中531人）は暫定値である。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合であることから、資料依頼No.5（指定事業所台帳）により定員をご提供いただく。受領後に第2章第3節の定員及び第7章第1節の把握率を更新する。</t>
+          <t>定員ベースの把握率74.1％（717人中531人）は暫定値である。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合であることから、資料依頼No.18（指定事業所台帳）により定員をご提供いただく。受領後に第2章第3節の定員及び第7章第1節の把握率を更新する。</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>発注者（指定事業所台帳・資料依頼No.5）</t>
+          <t>発注者（指定事業所台帳・資料依頼No.18）</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11579,7 +11579,7 @@
       <c r="G5" s="13" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>事業所票のQ1がすべて0、Q2以降が未記入</t>
+          <t>事業所票のQ1がすべて0、Q2以降が未記入。指定が令和7年10月1日であり基準日に未開設（点検No.7・解消）</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>居宅介護支援事業所おうか</t>
+          <t>居宅介護支援事業所おうか【解消】</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>事業所の休止・廃止か、記入漏れかを確認する。休止・廃止であれば第2章第3節の事業所数に影響する。</t>
+          <t>令和8年8月6日に受領した介護サービス情報公表システムの個別公表画面（記入日 令和8年2月11日）により、事業開始年月日及び指定年月日がいずれも令和7年10月1日であることを確認した。調査の基準日である令和7年4月1日時点では開設していない。したがって0は休止・廃止でも記入漏れでもなく、正しい状態である。在宅生活改善調査の集計対象からは除き、「回答事業所15件」と「集計に反映した事業所14件」を区別する。第2章第3節の事業所数には令和8年6月30日現在の13事業所として含める（住まいと施設の公表名簿との突合 07・10シート）。</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -12196,7 +12196,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。</t>
+          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。令和8年8月6日に受領したヘルパーステーションフラワーの公表画面（記入日 令和7年10月29日）により、訪問介護員等の実人数13人・常勤8人・非常勤5人、前年度の採用者数7人・退職者数2人が確認された。調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが裏づけられた（住まいと施設の公表名簿との突合 11シート）。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側が0であることを公表データで確かめることはできない。確定にはなお提出元への確認を要する。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち2事業所は公表画面を受領して把握済で、残りは8事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>訪問系の回収状況</t>
+          <t>訪問系の回収状況【一部解消】</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。13事業所との差が未回収であるのか、区域外の事業所を含む数であるのかを確認する。</t>
+          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち2事業所（ケンセイシャレバレッジ10人・東神楽町ホームヘルプサービスセンター6人）の訪問介護員等の実人数を把握した。13事業所のうち5事業所（回答3・未回答2）まで把握が進んだ。残る8事業所の公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち2事業所は公表画面を受領して把握済で、残りは8事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち3事業所は公表画面を受領して把握済で、残りは7事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。令和8年8月6日に受領したヘルパーステーションフラワーの公表画面（記入日 令和7年10月29日）により、訪問介護員等の実人数13人・常勤8人・非常勤5人、前年度の採用者数7人・退職者数2人が確認された。調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが裏づけられた（住まいと施設の公表名簿との突合 11シート）。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側が0であることを公表データで確かめることはできない。確定にはなお提出元への確認を要する。</t>
+          <t>2事業所の職員を単純に合計すると13人が二重に計上される。同じ構造の「有料老人ホームびえいの郷（1人）とシルバーハウス訪問介護事業所（13人）」は分けて記入されており、サービス付高齢者住宅ゆうも0人である。住宅型有料老人ホームは介護保険の指定サービスではなく、見える化のK系列にも従事者数の系列にも現れない（10シート）。併設の訪問介護が介護を提供する形であれば、実数は訪問系の13人であり、有料老人ホーム華の13人は重複となる。受託者は、訪問系13人を実数とし有料側を重複として除いた348人を用いることを案とする。実数を照会のうえ確定する。令和8年8月5日に受領したグループホームびえいの郷の公表画面により、シルバーハウス株式会社は訪問介護（美瑛町大町2丁目5番28号）とグループホーム（同5番14号）を別の所在地で運営し、住宅型有料老人ホームびえいの郷は訪問介護と同じ5番28号にあることが確認された。併設の訪問介護が介護を提供する構造が裏付けられた。令和8年8月6日に受領したヘルパーステーションフラワーの公表画面（記入日 令和7年10月29日）により、訪問介護員等の実人数13人・常勤8人・非常勤5人、前年度の採用者数7人・退職者数2人が確認された。調査の訪問系の票と実人数・常勤・非常勤・採用・離職のすべてが一致する。訪問介護事業所の側の13人が実在の値であることが裏づけられた（住まいと施設の公表名簿との突合 11シート）。ただし公表制度の対象は指定サービスであり、有料老人ホーム華（住宅型有料老人ホーム）は対象外であるため、華の側が0であることを公表データで確かめることはできない。確定にはなお提出元への確認を要する。なお、同じ構造の株式会社オレンジサポート（住宅型有料老人ホームひばりの森・グループホームひばり・指定訪問介護事業所ひばりが同一敷地）については、施設票の9人（常勤7・非常勤2・採用3・離職0）と訪問介護の公表画面の12人（常勤11・非常勤1・採用0・退職1）が異なる数値であり、転記ではない。ただし訪問介護12人のうち11人が兼務であるため、施設票の職員との重複の有無は確かめられていない。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち2事業所（ケンセイシャレバレッジ10人・東神楽町ホームヘルプサービスセンター6人）の訪問介護員等の実人数を把握した。13事業所のうち5事業所（回答3・未回答2）まで把握が進んだ。残る8事業所の公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。</t>
+          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち3事業所（ケンセイシャレバレッジ10人・東神楽町ホームヘルプサービスセンター6人・指定訪問介護事業所ひばり12人）の訪問介護員等の実人数を把握した。13事業所のうち6事業所（回答3・未回答3）・訪問介護員等74人まで把握が進んだ。残る7事業所の公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち3事業所は公表画面を受領して把握済で、残りは7事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち8事業所は公表画面を受領して把握済で、残りは2事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -13186,7 +13186,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち3事業所（ケンセイシャレバレッジ10人・東神楽町ホームヘルプサービスセンター6人・指定訪問介護事業所ひばり12人）の訪問介護員等の実人数を把握した。13事業所のうち6事業所（回答3・未回答3）・訪問介護員等74人まで把握が進んだ。残る7事業所の公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。</t>
+          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち8事業所の訪問介護員等の実人数を把握した。13事業所のうち11事業所（回答3・未回答8）・訪問介護員等158人まで把握が進んだ。残るのは訪問介護事業所 ほがらか及び指定訪問介護ステーション ゆうの2事業所であり、その公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。把握できた158人のうち122人（77.2％）が、住宅型有料老人ホーム又はサービス付き高齢者向け住宅に併設された7事業所に所属している。</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。うち8事業所は公表画面を受領して把握済で、残りは2事業所）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
+          <t>No.1（華の二重計上13人）、No.31（老健・通所リハと見える化の乖離）、No.15〜No.19（職員個票・職員票の枚数と介護職員数の差）、No.22（小規模多機能5事業所の職員数）、No.23（訪問介護13事業所のうち未回答10事業所の職員数。10事業所すべて公表画面を受領して把握済み）。点検事項35件のうち8件が、事業所への照会を待たずに解消できます。</t>
         </is>
       </c>
       <c r="C14" s="8" t="n"/>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>訪問系の回収状況【一部解消】</t>
+          <t>訪問系の回収状況【解消】</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所のうち8事業所の訪問介護員等の実人数を把握した。13事業所のうち11事業所（回答3・未回答8）・訪問介護員等158人まで把握が進んだ。残るのは訪問介護事業所 ほがらか及び指定訪問介護ステーション ゆうの2事業所であり、その公表画面を入手すれば全数の把握となる（住まいと施設の公表名簿との突合 11シート）。把握できた158人のうち122人（77.2％）が、住宅型有料老人ホーム又はサービス付き高齢者向け住宅に併設された7事業所に所属している。</t>
+          <t>訪問介護の人材分析は3事業所によるものであり、代表性に留意が必要である。本文では「回答のあった3事業所」と明記する。令和8年8月6日以降に受領した公表画面により、未回答10事業所すべての訪問介護員等の実人数を把握した。区域内の訪問介護13事業所すべて・訪問介護員等181人の全数が把握でき、代表性の限界は解消した（住まいと施設の公表名簿との突合 11シート）。計画本文の訪問介護の人材に関する記述は、調査の回答3事業所42人ではなく公表画面による181人を用いる。ただし公表画面の記入日は令和7年10月3日から11月7日までであり、調査の基準日（令和7年4月1日）と時点が異なるため、本文では「令和7年10〜11月時点」と明記する。181人のうち128人（70.7％）が、住宅型有料老人ホーム、サービス付き高齢者向け住宅又は介護付有料老人ホームに併設された8事業所に所属している。</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">

--- a/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
+++ b/output/第10期計画_実施済み3調査の受領点検と集計.xlsx
@@ -22379,7 +22379,7 @@
     <row r="51" ht="104" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>注1）介護人材実態調査の自由回答では、人材紹介会社への紹介料が経営を圧迫しているという記述が5法人から寄せられている。「1名雇用するのにその人の年収30％の手数料」「1名正職員採用で70〜80万円」という具体的な金額の記述がある。注2）外国人材については、受入れの拡大と定着の難しさがいずれも記述されている。「関東地方より賃金が低いため1年ほどで移動の希望がある」との指摘がある。注3）美瑛町の福祉人材確保の交付金について「人材確保と定着に大きなサポート」としつつ「交付金が切れる頃、約1年ほどで辞めてしまう方もいる」との指摘がある。第5章の人材施策の設計に用いる。注4）居所変更実態調査の自由回答では、18施設のうち多くが「医療的ニーズの高まりによる入院と、そのまま退去となるケース」を挙げている。05シートの退去先・退去理由の集計と整合する。</t>
+          <t>注1）介護人材実態調査の自由回答では、人材紹介会社への紹介料が経営を圧迫しているという記述が5法人から寄せられている。「1名雇用するのにその人の年収30％の手数料」「1名正職員採用で70〜80万円」という具体的な金額の記述がある。注2）外国人材については、受入れの拡大と定着の難しさがいずれも記述されている。「関東地方より賃金が低いため1年ほどで移動の希望がある」との指摘がある。注3）美瑛町の福祉人材確保の交付金について「人材確保と定着に大きなサポート」としつつ「交付金が切れる頃、約1年ほどで辞めてしまう方もいる」との指摘がある。第5章の人材施策の設計に用いる。注4）居所変更実態調査の自由回答では、18施設のうち多くが「医療的ニーズの高まりによる入院と、そのまま退去となるケース」を挙げている。05シートの退去先・退去理由の集計と符合する。</t>
         </is>
       </c>
     </row>
